--- a/data/excel/ebidta-calculation.xlsx
+++ b/data/excel/ebidta-calculation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MatthiasLavenant\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F077BFDA-D5CA-48DB-88CA-0E2840303001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D073A4B-6F54-4149-8D0E-BB1C40223030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4D0FF4E0-719F-4FA7-A162-20EBE03DBE4E}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4D0FF4E0-719F-4FA7-A162-20EBE03DBE4E}"/>
   </bookViews>
   <sheets>
     <sheet name="EBIDTA 2" sheetId="1" r:id="rId1"/>
@@ -1655,28 +1655,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="15" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="15" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1697,8 +1676,29 @@
     <xf numFmtId="2" fontId="6" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="15" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5714,11 +5714,11 @@
     </row>
     <row r="2" spans="2:175" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C2" s="2"/>
-      <c r="D2" s="85">
+      <c r="D2" s="78">
         <f>'[1]Overview 2026'!B24</f>
         <v>46025</v>
       </c>
-      <c r="E2" s="85"/>
+      <c r="E2" s="78"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2"/>
@@ -6070,11 +6070,11 @@
         <f>'[1]Overview 2026'!J3</f>
         <v>9</v>
       </c>
-      <c r="D4" s="86" t="str">
+      <c r="D4" s="79" t="str">
         <f>VLOOKUP(D$2,'[1]Overview 2026'!$B$7:$AC$52,$C4,FALSE)</f>
         <v>CLOONEE</v>
       </c>
-      <c r="E4" s="86"/>
+      <c r="E4" s="79"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4"/>
@@ -6254,11 +6254,11 @@
         <f>'[1]Overview 2026'!L3</f>
         <v>11</v>
       </c>
-      <c r="D5" s="87">
+      <c r="D5" s="80">
         <f>VLOOKUP(D$2,'[1]Overview 2026'!$B$7:$AC$52,$C5,FALSE)</f>
         <v>100000</v>
       </c>
-      <c r="E5" s="88"/>
+      <c r="E5" s="81"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
       <c r="H5"/>
@@ -6435,11 +6435,11 @@
         <v>1</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="89">
+      <c r="D6" s="82">
         <f>IFERROR(D5/D8,"")</f>
         <v>0.45454545454545453</v>
       </c>
-      <c r="E6" s="90"/>
+      <c r="E6" s="83"/>
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="H6"/>
@@ -6794,11 +6794,11 @@
         <f>'[1]Overview 2026'!F3</f>
         <v>5</v>
       </c>
-      <c r="D8" s="91">
+      <c r="D8" s="77">
         <f>D15+D16</f>
         <v>220000</v>
       </c>
-      <c r="E8" s="91"/>
+      <c r="E8" s="77"/>
     </row>
     <row r="9" spans="2:175" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
@@ -6808,22 +6808,22 @@
         <f>'[1]Overview 2026'!H3</f>
         <v>7</v>
       </c>
-      <c r="D9" s="91">
+      <c r="D9" s="77">
         <f>VLOOKUP(D$2,'[1]Overview 2026'!$B$7:$AC$52,$C9,FALSE)</f>
         <v>101500</v>
       </c>
-      <c r="E9" s="91"/>
+      <c r="E9" s="77"/>
     </row>
     <row r="10" spans="2:175" x14ac:dyDescent="0.25">
       <c r="B10" s="14" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="15"/>
-      <c r="D10" s="80">
+      <c r="D10" s="85">
         <f>SUM(D8:E9)</f>
         <v>321500</v>
       </c>
-      <c r="E10" s="80"/>
+      <c r="E10" s="85"/>
     </row>
     <row r="11" spans="2:175" x14ac:dyDescent="0.25">
       <c r="B11" s="16" t="s">
@@ -6833,11 +6833,11 @@
         <f>'[1]Overview 2026'!D3</f>
         <v>3</v>
       </c>
-      <c r="D11" s="81" t="str">
+      <c r="D11" s="86" t="str">
         <f>IF(VLOOKUP(D$2,'[1]Overview 2026'!$B6:$AC$52,$C11,FALSE)=0,"",VLOOKUP(D$2,'[1]Overview 2026'!$B6:$AC$52,$C11,FALSE))</f>
         <v/>
       </c>
-      <c r="E11" s="81"/>
+      <c r="E11" s="86"/>
     </row>
     <row r="12" spans="2:175" x14ac:dyDescent="0.25">
       <c r="B12" s="16" t="s">
@@ -6847,11 +6847,11 @@
         <f>'[1]Overview 2026'!C3</f>
         <v>2</v>
       </c>
-      <c r="D12" s="81" t="str">
+      <c r="D12" s="86" t="str">
         <f>IF(VLOOKUP(D$2,'[1]Overview 2026'!$B7:$AC$52,$C12,FALSE)=0,"",VLOOKUP(D$2,'[1]Overview 2026'!$B7:$AC$52,$C12,FALSE))</f>
         <v/>
       </c>
-      <c r="E12" s="81"/>
+      <c r="E12" s="86"/>
     </row>
     <row r="13" spans="2:175" x14ac:dyDescent="0.25">
       <c r="B13" s="18"/>
@@ -6914,11 +6914,11 @@
       <c r="B19" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="82">
+      <c r="D19" s="87">
         <f>E30</f>
         <v>28</v>
       </c>
-      <c r="E19" s="82"/>
+      <c r="E19" s="87"/>
       <c r="F19" s="29"/>
       <c r="G19" s="29"/>
     </row>
@@ -6926,11 +6926,11 @@
       <c r="B20" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="83">
+      <c r="D20" s="88">
         <f>D16/D19</f>
         <v>7142.8571428571431</v>
       </c>
-      <c r="E20" s="83"/>
+      <c r="E20" s="88"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="18"/>
@@ -6943,11 +6943,11 @@
         <f>'[1]Overview 2026'!R3</f>
         <v>17</v>
       </c>
-      <c r="D22" s="84" t="str">
+      <c r="D22" s="89" t="str">
         <f>IF(VLOOKUP(D$2,'[1]Overview 2026'!$B$7:$AC$52,$C22,FALSE)=0,"Beach Club",VLOOKUP(D$2,'[1]Overview 2026'!$B$7:$AC$52,$C22,FALSE))</f>
         <v>Beach Club</v>
       </c>
-      <c r="E22" s="84"/>
+      <c r="E22" s="89"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="str">
@@ -7665,11 +7665,11 @@
       </c>
       <c r="D53" s="25">
         <f>'OPEX DATA 2'!U161</f>
-        <v>6.8461538461538463E-2</v>
+        <v>5.8681318681318685E-2</v>
       </c>
       <c r="E53" s="13">
         <f t="shared" ref="E53:E101" si="3">D53/D$36</f>
-        <v>2.1294413207321449E-7</v>
+        <v>1.82523541777041E-7</v>
       </c>
     </row>
     <row r="54" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7679,11 +7679,11 @@
       </c>
       <c r="D54" s="25">
         <f>'OPEX DATA 2'!U162</f>
-        <v>484.85557692307697</v>
+        <v>415.59049450549452</v>
       </c>
       <c r="E54" s="13">
         <f t="shared" si="3"/>
-        <v>1.5081044383299439E-3</v>
+        <v>1.2926609471399519E-3</v>
       </c>
     </row>
     <row r="55" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7693,11 +7693,11 @@
       </c>
       <c r="D55" s="25">
         <f>'OPEX DATA 2'!U163</f>
-        <v>458.92115384615386</v>
+        <v>393.36098901098904</v>
       </c>
       <c r="E55" s="13">
         <f t="shared" si="3"/>
-        <v>1.427437492523029E-3</v>
+        <v>1.223517850734025E-3</v>
       </c>
     </row>
     <row r="56" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7707,11 +7707,11 @@
       </c>
       <c r="D56" s="25">
         <f>'OPEX DATA 2'!U164</f>
-        <v>40.874487179487183</v>
+        <v>35.035274725274725</v>
       </c>
       <c r="E56" s="13">
         <f t="shared" si="3"/>
-        <v>1.2713681859871596E-4</v>
+        <v>1.0897441594175653E-4</v>
       </c>
     </row>
     <row r="57" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7721,11 +7721,11 @@
       </c>
       <c r="D57" s="25">
         <f>'OPEX DATA 2'!U165</f>
-        <v>63.936538461538468</v>
+        <v>54.80274725274726</v>
       </c>
       <c r="E57" s="13">
         <f t="shared" si="3"/>
-        <v>1.9886948199545403E-4</v>
+        <v>1.7045955599610346E-4</v>
       </c>
     </row>
     <row r="58" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7735,11 +7735,11 @@
       </c>
       <c r="D58" s="25">
         <f>'OPEX DATA 2'!U166</f>
-        <v>283.37769230769237</v>
+        <v>242.89516483516488</v>
       </c>
       <c r="E58" s="13">
         <f t="shared" si="3"/>
-        <v>8.8142361526498403E-4</v>
+        <v>7.5550595594141485E-4</v>
       </c>
     </row>
     <row r="59" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7749,11 +7749,11 @@
       </c>
       <c r="D59" s="25">
         <f>'OPEX DATA 2'!U167</f>
-        <v>257.25012820512819</v>
+        <v>220.50010989010985</v>
       </c>
       <c r="E59" s="13">
         <f t="shared" si="3"/>
-        <v>8.0015591976711727E-4</v>
+        <v>6.8584793122895751E-4</v>
       </c>
     </row>
     <row r="60" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7763,11 +7763,11 @@
       </c>
       <c r="D60" s="25">
         <f>'OPEX DATA 2'!U168</f>
-        <v>578.48634615384606</v>
+        <v>495.8454395604395</v>
       </c>
       <c r="E60" s="13">
         <f t="shared" si="3"/>
-        <v>1.7993354468237824E-3</v>
+        <v>1.5422875258489564E-3</v>
       </c>
     </row>
     <row r="61" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7777,11 +7777,11 @@
       </c>
       <c r="D61" s="25">
         <f>'OPEX DATA 2'!U169</f>
-        <v>52.883461538461539</v>
+        <v>45.328681318681319</v>
       </c>
       <c r="E61" s="13">
         <f t="shared" si="3"/>
-        <v>1.644897715037684E-4</v>
+        <v>1.4099123271751576E-4</v>
       </c>
     </row>
     <row r="62" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7791,11 +7791,11 @@
       </c>
       <c r="D62" s="25">
         <f>'OPEX DATA 2'!U170</f>
-        <v>551.14230769230767</v>
+        <v>472.40769230769229</v>
       </c>
       <c r="E62" s="13">
         <f t="shared" si="3"/>
-        <v>1.7142840052637874E-3</v>
+        <v>1.4693862902261036E-3</v>
       </c>
     </row>
     <row r="63" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7805,11 +7805,11 @@
       </c>
       <c r="D63" s="25">
         <f>'OPEX DATA 2'!U171</f>
-        <v>481.61756410256407</v>
+        <v>412.8150549450549</v>
       </c>
       <c r="E63" s="13">
         <f t="shared" si="3"/>
-        <v>1.4980328587949115E-3</v>
+        <v>1.2840281646813527E-3</v>
       </c>
     </row>
     <row r="64" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7833,11 +7833,11 @@
       </c>
       <c r="D65" s="25">
         <f>'OPEX DATA 2'!U173</f>
-        <v>2.4183974358974356</v>
+        <v>2.0729120879120879</v>
       </c>
       <c r="E65" s="13">
         <f t="shared" si="3"/>
-        <v>7.5222315268971561E-6</v>
+        <v>6.4476270230547058E-6</v>
       </c>
     </row>
     <row r="66" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7847,11 +7847,11 @@
       </c>
       <c r="D66" s="25">
         <f>'OPEX DATA 2'!U174</f>
-        <v>29.191794871794873</v>
+        <v>25.021538461538462</v>
       </c>
       <c r="E66" s="13">
         <f t="shared" si="3"/>
-        <v>9.0798739881166012E-5</v>
+        <v>7.7827491326713728E-5</v>
       </c>
     </row>
     <row r="67" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7861,11 +7861,11 @@
       </c>
       <c r="D67" s="25">
         <f>'OPEX DATA 2'!U175</f>
-        <v>278.46621794871794</v>
+        <v>238.68532967032965</v>
       </c>
       <c r="E67" s="13">
         <f t="shared" si="3"/>
-        <v>8.6614686764764518E-4</v>
+        <v>7.4241160084083868E-4</v>
       </c>
     </row>
     <row r="68" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7875,11 +7875,11 @@
       </c>
       <c r="D68" s="25">
         <f>'OPEX DATA 2'!U176</f>
-        <v>215.20608974358973</v>
+        <v>184.46236263736265</v>
       </c>
       <c r="E68" s="13">
         <f t="shared" si="3"/>
-        <v>6.6938130557881717E-4</v>
+        <v>5.7375540478184336E-4</v>
       </c>
     </row>
     <row r="69" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7889,11 +7889,11 @@
       </c>
       <c r="D69" s="25">
         <f>'OPEX DATA 2'!U177</f>
-        <v>468.93128205128204</v>
+        <v>401.94109890109888</v>
       </c>
       <c r="E69" s="13">
         <f t="shared" si="3"/>
-        <v>1.4585731945607528E-3</v>
+        <v>1.2502055953377881E-3</v>
       </c>
     </row>
     <row r="70" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7903,11 +7903,11 @@
       </c>
       <c r="D70" s="25">
         <f>'OPEX DATA 2'!U178</f>
-        <v>531.62153846153853</v>
+        <v>455.67560439560441</v>
       </c>
       <c r="E70" s="13">
         <f t="shared" si="3"/>
-        <v>1.6535662160545523E-3</v>
+        <v>1.4173424709039018E-3</v>
       </c>
     </row>
     <row r="71" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7917,11 +7917,11 @@
       </c>
       <c r="D71" s="25">
         <f>'OPEX DATA 2'!U179</f>
-        <v>225.84070512820514</v>
+        <v>193.57774725274726</v>
       </c>
       <c r="E71" s="13">
         <f t="shared" si="3"/>
-        <v>7.0245942497108914E-4</v>
+        <v>6.0210807854664777E-4</v>
       </c>
     </row>
     <row r="72" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7931,11 +7931,11 @@
       </c>
       <c r="D72" s="25">
         <f>'OPEX DATA 2'!U180</f>
-        <v>1459.2776923076924</v>
+        <v>1250.8094505494505</v>
       </c>
       <c r="E72" s="13">
         <f t="shared" si="3"/>
-        <v>4.538966383538701E-3</v>
+        <v>3.8905426144617435E-3</v>
       </c>
     </row>
     <row r="73" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7945,11 +7945,11 @@
       </c>
       <c r="D73" s="25">
         <f>'OPEX DATA 2'!U181</f>
-        <v>6.4102564102564097</v>
+        <v>5.4945054945054945</v>
       </c>
       <c r="E73" s="13">
         <f t="shared" si="3"/>
-        <v>1.9938589145432066E-5</v>
+        <v>1.7090219267513201E-5</v>
       </c>
     </row>
     <row r="74" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7959,11 +7959,11 @@
       </c>
       <c r="D74" s="25">
         <f>'OPEX DATA 2'!U182</f>
-        <v>9.4361538461538448</v>
+        <v>8.0881318681318675</v>
       </c>
       <c r="E74" s="13">
         <f t="shared" si="3"/>
-        <v>2.9350400765641818E-5</v>
+        <v>2.5157486370550131E-5</v>
       </c>
     </row>
     <row r="75" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7973,11 +7973,11 @@
       </c>
       <c r="D75" s="25">
         <f>'OPEX DATA 2'!U183</f>
-        <v>284.31608974358971</v>
+        <v>243.69950549450547</v>
       </c>
       <c r="E75" s="13">
         <f t="shared" si="3"/>
-        <v>8.8434242532998357E-4</v>
+        <v>7.5800779313998587E-4</v>
       </c>
     </row>
     <row r="76" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7987,11 +7987,11 @@
       </c>
       <c r="D76" s="25">
         <f>'OPEX DATA 2'!U184</f>
-        <v>29.522628205128203</v>
+        <v>25.30510989010989</v>
       </c>
       <c r="E76" s="13">
         <f t="shared" si="3"/>
-        <v>9.1827770466961756E-5</v>
+        <v>7.8709517543110074E-5</v>
       </c>
     </row>
     <row r="77" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8001,11 +8001,11 @@
       </c>
       <c r="D77" s="25">
         <f>'OPEX DATA 2'!U185</f>
-        <v>58.050961538461543</v>
+        <v>49.757967032967038</v>
       </c>
       <c r="E77" s="13">
         <f t="shared" si="3"/>
-        <v>1.8056286637157555E-4</v>
+        <v>1.547681711756362E-4</v>
       </c>
     </row>
     <row r="78" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8029,11 +8029,11 @@
       </c>
       <c r="D79" s="25">
         <f>'OPEX DATA 2'!U187</f>
-        <v>164.26801282051284</v>
+        <v>140.80115384615385</v>
       </c>
       <c r="E79" s="13">
         <f t="shared" si="3"/>
-        <v>5.1094249710890462E-4</v>
+        <v>4.3795071180763252E-4</v>
       </c>
     </row>
     <row r="80" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8043,11 +8043,11 @@
       </c>
       <c r="D80" s="25">
         <f>'OPEX DATA 2'!U188</f>
-        <v>263.00173076923073</v>
+        <v>225.43005494505493</v>
       </c>
       <c r="E80" s="13">
         <f t="shared" si="3"/>
-        <v>8.1804581887785614E-4</v>
+        <v>7.0118213046673383E-4</v>
       </c>
     </row>
     <row r="81" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8057,11 +8057,11 @@
       </c>
       <c r="D81" s="25">
         <f>'OPEX DATA 2'!U189</f>
-        <v>816.73032051282053</v>
+        <v>700.05456043956042</v>
       </c>
       <c r="E81" s="13">
         <f t="shared" si="3"/>
-        <v>2.5403742473182598E-3</v>
+        <v>2.1774636405585083E-3</v>
       </c>
     </row>
     <row r="82" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8071,11 +8071,11 @@
       </c>
       <c r="D82" s="25">
         <f>'OPEX DATA 2'!U190</f>
-        <v>46.427115384615384</v>
+        <v>39.794670329670332</v>
       </c>
       <c r="E82" s="13">
         <f t="shared" si="3"/>
-        <v>1.4440782390238066E-4</v>
+        <v>1.2377813477346914E-4</v>
       </c>
     </row>
     <row r="83" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8099,11 +8099,11 @@
       </c>
       <c r="D84" s="25">
         <f>'OPEX DATA 2'!U192</f>
-        <v>335.17160256410256</v>
+        <v>287.28994505494501</v>
       </c>
       <c r="E84" s="13">
         <f t="shared" si="3"/>
-        <v>1.0425244247717032E-3</v>
+        <v>8.9359236409003115E-4</v>
       </c>
     </row>
     <row r="85" spans="2:175" x14ac:dyDescent="0.25">
@@ -8114,11 +8114,11 @@
       <c r="C85" s="15"/>
       <c r="D85" s="33">
         <f>'OPEX DATA 2'!U193</f>
-        <v>1651.3973076923078</v>
+        <v>1415.4834065934067</v>
       </c>
       <c r="E85" s="34">
         <f t="shared" si="3"/>
-        <v>5.1365390596961359E-3</v>
+        <v>4.4027477654538308E-3</v>
       </c>
     </row>
     <row r="86" spans="2:175" x14ac:dyDescent="0.25">
@@ -8128,11 +8128,11 @@
       </c>
       <c r="D86" s="25">
         <f>'OPEX DATA 2'!U194</f>
-        <v>803.67128205128199</v>
+        <v>688.86109890109879</v>
       </c>
       <c r="E86" s="13">
         <f t="shared" si="3"/>
-        <v>2.4997551541252939E-3</v>
+        <v>2.1426472749645374E-3</v>
       </c>
     </row>
     <row r="87" spans="2:175" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8143,11 +8143,11 @@
       <c r="C87" s="2"/>
       <c r="D87" s="19">
         <f>'OPEX DATA 2'!U195</f>
-        <v>69.340384615384608</v>
+        <v>59.434615384615377</v>
       </c>
       <c r="E87" s="12">
         <f t="shared" si="3"/>
-        <v>2.1567771264505321E-4</v>
+        <v>1.8486661083861705E-4</v>
       </c>
       <c r="F87" s="12"/>
       <c r="G87" s="12"/>
@@ -8341,11 +8341,11 @@
       </c>
       <c r="D89" s="25">
         <f>'OPEX DATA 2'!U197</f>
-        <v>1.3653846153846154E-2</v>
+        <v>1.1703296703296702E-2</v>
       </c>
       <c r="E89" s="13">
         <f t="shared" si="3"/>
-        <v>4.2469194879770304E-8</v>
+        <v>3.6402167039803118E-8</v>
       </c>
     </row>
     <row r="90" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8397,11 +8397,11 @@
       </c>
       <c r="D93" s="25">
         <f>'OPEX DATA 2'!U201</f>
-        <v>60.913525641025643</v>
+        <v>52.211593406593408</v>
       </c>
       <c r="E93" s="13">
         <f t="shared" si="3"/>
-        <v>1.8946664274035969E-4</v>
+        <v>1.6239997949173688E-4</v>
       </c>
     </row>
     <row r="94" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8510,11 +8510,11 @@
       <c r="C101" s="36"/>
       <c r="D101" s="37">
         <f>SUM(D53:D100)</f>
-        <v>111063.03846153845</v>
+        <v>109482.6043956044</v>
       </c>
       <c r="E101" s="38">
         <f t="shared" si="3"/>
-        <v>0.34545268572795784</v>
+        <v>0.34053687214806966</v>
       </c>
       <c r="F101" s="38"/>
       <c r="G101" s="38"/>
@@ -8550,11 +8550,11 @@
       </c>
       <c r="D105" s="25">
         <f>'OPEX DATA 2'!U216</f>
-        <v>252.40237179487178</v>
+        <v>216.34489010989009</v>
       </c>
       <c r="E105" s="13">
         <f t="shared" ref="E105:E130" si="4">D105/D$36</f>
-        <v>7.8507736172588429E-4</v>
+        <v>6.7292345290790071E-4</v>
       </c>
     </row>
     <row r="106" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8564,11 +8564,11 @@
       </c>
       <c r="D106" s="25">
         <f>'OPEX DATA 2'!U217</f>
-        <v>688.54916666666668</v>
+        <v>590.18500000000006</v>
       </c>
       <c r="E106" s="13">
         <f t="shared" si="4"/>
-        <v>2.1416770347330223E-3</v>
+        <v>1.8357231726283049E-3</v>
       </c>
     </row>
     <row r="107" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8578,11 +8578,11 @@
       </c>
       <c r="D107" s="25">
         <f>'OPEX DATA 2'!U218</f>
-        <v>221.89397435897436</v>
+        <v>190.19483516483518</v>
       </c>
       <c r="E107" s="13">
         <f t="shared" si="4"/>
-        <v>6.90183435020138E-4</v>
+        <v>5.915858014458326E-4</v>
       </c>
     </row>
     <row r="108" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8592,11 +8592,11 @@
       </c>
       <c r="D108" s="25">
         <f>'OPEX DATA 2'!U219</f>
-        <v>1762.2203846153845</v>
+        <v>1510.4746153846154</v>
       </c>
       <c r="E108" s="13">
         <f t="shared" si="4"/>
-        <v>5.4812453642780236E-3</v>
+        <v>4.6982103122383059E-3</v>
       </c>
     </row>
     <row r="109" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8606,11 +8606,11 @@
       </c>
       <c r="D109" s="25">
         <f>'OPEX DATA 2'!U220</f>
-        <v>3.8497435897435914</v>
+        <v>3.2997802197802213</v>
       </c>
       <c r="E109" s="13">
         <f t="shared" si="4"/>
-        <v>1.1974319097180688E-5</v>
+        <v>1.0263702083297733E-5</v>
       </c>
     </row>
     <row r="110" spans="2:175" x14ac:dyDescent="0.25">
@@ -8621,11 +8621,11 @@
       <c r="C110" s="15"/>
       <c r="D110" s="33">
         <f>'OPEX DATA 2'!U221</f>
-        <v>339.23352564102566</v>
+        <v>290.77159340659341</v>
       </c>
       <c r="E110" s="34">
         <f t="shared" si="4"/>
-        <v>1.0551587111695977E-3</v>
+        <v>9.0442175243108367E-4</v>
       </c>
     </row>
     <row r="111" spans="2:175" x14ac:dyDescent="0.25">
@@ -8635,11 +8635,11 @@
       </c>
       <c r="D111" s="25">
         <f>'OPEX DATA 2'!U222</f>
-        <v>37.305128205128206</v>
+        <v>31.975824175824179</v>
       </c>
       <c r="E111" s="13">
         <f t="shared" si="4"/>
-        <v>1.1603461339075648E-4</v>
+        <v>9.9458240049219836E-5</v>
       </c>
     </row>
     <row r="112" spans="2:175" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -8650,11 +8650,11 @@
       <c r="C112" s="2"/>
       <c r="D112" s="19">
         <f>'OPEX DATA 2'!U223</f>
-        <v>25.710576923076925</v>
+        <v>22.037637362637362</v>
       </c>
       <c r="E112" s="12">
         <f t="shared" si="4"/>
-        <v>7.9970690273956221E-5</v>
+        <v>6.8546305949105328E-5</v>
       </c>
       <c r="F112" s="12"/>
       <c r="G112" s="12"/>
@@ -8834,11 +8834,11 @@
       </c>
       <c r="D113" s="25">
         <f>'OPEX DATA 2'!U224</f>
-        <v>7.3519230769230779</v>
+        <v>6.3016483516483524</v>
       </c>
       <c r="E113" s="13">
         <f t="shared" si="4"/>
-        <v>2.2867567890896044E-5</v>
+        <v>1.9600772477910894E-5</v>
       </c>
     </row>
     <row r="114" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8848,11 +8848,11 @@
       </c>
       <c r="D114" s="25">
         <f>'OPEX DATA 2'!U225</f>
-        <v>12.870384615384616</v>
+        <v>11.031758241758242</v>
       </c>
       <c r="E114" s="13">
         <f t="shared" si="4"/>
-        <v>4.0032300514415604E-5</v>
+        <v>3.4313400440927659E-5</v>
       </c>
     </row>
     <row r="115" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8862,11 +8862,11 @@
       </c>
       <c r="D115" s="25">
         <f>'OPEX DATA 2'!U226</f>
-        <v>-0.15576923076923122</v>
+        <v>-0.1335164835164839</v>
       </c>
       <c r="E115" s="13">
         <f t="shared" si="4"/>
-        <v>-4.845077162340007E-7</v>
+        <v>-4.1529232820057204E-7</v>
       </c>
     </row>
     <row r="116" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8876,11 +8876,11 @@
       </c>
       <c r="D116" s="25">
         <f>'OPEX DATA 2'!U227</f>
-        <v>198.41711538461541</v>
+        <v>170.07181318681322</v>
       </c>
       <c r="E116" s="13">
         <f t="shared" si="4"/>
-        <v>6.171605455197991E-4</v>
+        <v>5.2899475330268496E-4</v>
       </c>
     </row>
     <row r="117" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8890,11 +8890,11 @@
       </c>
       <c r="D117" s="25">
         <f>'OPEX DATA 2'!U228</f>
-        <v>68.685961538461541</v>
+        <v>58.873681318681314</v>
       </c>
       <c r="E117" s="13">
         <f t="shared" si="4"/>
-        <v>2.1364218207919609E-4</v>
+        <v>1.8312187035359663E-4</v>
       </c>
     </row>
     <row r="118" spans="2:175" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -8904,11 +8904,11 @@
       </c>
       <c r="D118" s="25">
         <f>'OPEX DATA 2'!U229</f>
-        <v>1.2692307692307692</v>
+        <v>1.0879120879120878</v>
       </c>
       <c r="E118" s="13">
         <f t="shared" si="4"/>
-        <v>3.9478406507955499E-6</v>
+        <v>3.3838634149676136E-6</v>
       </c>
     </row>
     <row r="119" spans="2:175" x14ac:dyDescent="0.25">
@@ -8919,11 +8919,11 @@
       <c r="C119" s="15"/>
       <c r="D119" s="33">
         <f>'OPEX DATA 2'!U230</f>
-        <v>282.94333333333333</v>
+        <v>242.52285714285713</v>
       </c>
       <c r="E119" s="34">
         <f t="shared" si="4"/>
-        <v>8.800725764644894E-4</v>
+        <v>7.5434792268384799E-4</v>
       </c>
     </row>
     <row r="120" spans="2:175" x14ac:dyDescent="0.25">
@@ -8948,11 +8948,11 @@
       <c r="C121" s="2"/>
       <c r="D121" s="19">
         <f>'OPEX DATA 2'!U232</f>
-        <v>101.28205128205128</v>
+        <v>86.813186813186817</v>
       </c>
       <c r="E121" s="12">
         <f t="shared" si="4"/>
-        <v>3.1502970849782669E-4</v>
+        <v>2.7002546442670859E-4</v>
       </c>
       <c r="F121" s="12"/>
       <c r="G121" s="12"/>
@@ -9133,11 +9133,11 @@
       <c r="C122" s="15"/>
       <c r="D122" s="33">
         <f>'OPEX DATA 2'!U233</f>
-        <v>20.954102564102566</v>
+        <v>17.96065934065934</v>
       </c>
       <c r="E122" s="34">
         <f t="shared" si="4"/>
-        <v>6.5176057742154171E-5</v>
+        <v>5.5865192350417855E-5</v>
       </c>
     </row>
     <row r="123" spans="2:175" x14ac:dyDescent="0.25">
@@ -9147,11 +9147,11 @@
       </c>
       <c r="D123" s="25">
         <f>'OPEX DATA 2'!U234</f>
-        <v>22.657884615384617</v>
+        <v>19.421043956043956</v>
       </c>
       <c r="E123" s="13">
         <f t="shared" si="4"/>
-        <v>7.0475535351118557E-5</v>
+        <v>6.0407601729530189E-5</v>
       </c>
     </row>
     <row r="124" spans="2:175" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9162,11 +9162,11 @@
       <c r="C124" s="2"/>
       <c r="D124" s="19">
         <f>'OPEX DATA 2'!U235</f>
-        <v>100.42314102564103</v>
+        <v>86.076978021978022</v>
       </c>
       <c r="E124" s="12">
         <f t="shared" si="4"/>
-        <v>3.1235813693823028E-4</v>
+        <v>2.677355459470545E-4</v>
       </c>
       <c r="F124" s="12"/>
       <c r="G124" s="12"/>
@@ -9346,11 +9346,11 @@
       </c>
       <c r="D125" s="25">
         <f>'OPEX DATA 2'!U236</f>
-        <v>1611.9710897435898</v>
+        <v>1381.6895054945055</v>
       </c>
       <c r="E125" s="13">
         <f t="shared" si="4"/>
-        <v>5.0139069665430473E-3</v>
+        <v>4.2976345427511832E-3</v>
       </c>
     </row>
     <row r="126" spans="2:175" x14ac:dyDescent="0.25">
@@ -9361,11 +9361,11 @@
       <c r="C126" s="15"/>
       <c r="D126" s="33">
         <f>'OPEX DATA 2'!U237</f>
-        <v>570.73942307692312</v>
+        <v>489.20521978021981</v>
       </c>
       <c r="E126" s="34">
         <f t="shared" si="4"/>
-        <v>1.7752392630697453E-3</v>
+        <v>1.5216336540597817E-3</v>
       </c>
     </row>
     <row r="127" spans="2:175" x14ac:dyDescent="0.25">
@@ -9375,11 +9375,11 @@
       </c>
       <c r="D127" s="25">
         <f>'OPEX DATA 2'!U238</f>
-        <v>27.217307692307696</v>
+        <v>23.329120879120882</v>
       </c>
       <c r="E127" s="13">
         <f t="shared" si="4"/>
-        <v>8.4657255652590039E-5</v>
+        <v>7.2563361987934314E-5</v>
       </c>
     </row>
     <row r="128" spans="2:175" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -9390,11 +9390,11 @@
       <c r="C128" s="2"/>
       <c r="D128" s="19">
         <f>'OPEX DATA 2'!U239</f>
-        <v>102.01923076923077</v>
+        <v>87.445054945054949</v>
       </c>
       <c r="E128" s="12">
         <f t="shared" si="4"/>
-        <v>3.1732264624955141E-4</v>
+        <v>2.7199083964247263E-4</v>
       </c>
       <c r="F128" s="12"/>
       <c r="G128" s="12"/>
@@ -9589,11 +9589,11 @@
       <c r="C130" s="36"/>
       <c r="D130" s="37">
         <f>SUM(D104:D129)</f>
-        <v>16104.81128205128</v>
+        <v>15181.9810989011</v>
       </c>
       <c r="E130" s="38">
         <f t="shared" si="4"/>
-        <v>5.0092725605136175E-2</v>
+        <v>4.7222336232973873E-2</v>
       </c>
       <c r="F130" s="38"/>
       <c r="G130" s="38"/>
@@ -9616,11 +9616,11 @@
       </c>
       <c r="D133" s="25">
         <f>'OPEX DATA 2'!U244</f>
-        <v>52.52346153846154</v>
+        <v>45.020109890109893</v>
       </c>
       <c r="E133" s="13">
         <f t="shared" ref="E133:E141" si="5">D133/D$36</f>
-        <v>1.6337002033736092E-4</v>
+        <v>1.4003144600345223E-4</v>
       </c>
     </row>
     <row r="134" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -9630,11 +9630,11 @@
       </c>
       <c r="D134" s="25">
         <f>'OPEX DATA 2'!U245</f>
-        <v>73.380384615384614</v>
+        <v>62.89747252747253</v>
       </c>
       <c r="E134" s="13">
         <f t="shared" si="5"/>
-        <v>2.2824380906807034E-4</v>
+        <v>1.9563755062977458E-4</v>
       </c>
     </row>
     <row r="135" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -9658,11 +9658,11 @@
       </c>
       <c r="D136" s="25">
         <f>'OPEX DATA 2'!U247</f>
-        <v>513.49512820512814</v>
+        <v>440.13868131868128</v>
       </c>
       <c r="E136" s="13">
         <f t="shared" si="5"/>
-        <v>1.5971854687562305E-3</v>
+        <v>1.3690161160767691E-3</v>
       </c>
     </row>
     <row r="137" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -9672,11 +9672,11 @@
       </c>
       <c r="D137" s="25">
         <f>'OPEX DATA 2'!U248</f>
-        <v>83.17532051282052</v>
+        <v>71.29313186813188</v>
       </c>
       <c r="E137" s="13">
         <f t="shared" si="5"/>
-        <v>2.5871017266818199E-4</v>
+        <v>2.2175157657272745E-4</v>
       </c>
     </row>
     <row r="138" spans="2:7" x14ac:dyDescent="0.25">
@@ -9687,11 +9687,11 @@
       <c r="C138" s="15"/>
       <c r="D138" s="33">
         <f>'OPEX DATA 2'!U249</f>
-        <v>269.22519230769228</v>
+        <v>230.76445054945052</v>
       </c>
       <c r="E138" s="34">
         <f t="shared" si="5"/>
-        <v>8.3740339753559029E-4</v>
+        <v>7.1777434074479167E-4</v>
       </c>
     </row>
     <row r="139" spans="2:7" x14ac:dyDescent="0.25">
@@ -9701,11 +9701,11 @@
       </c>
       <c r="D139" s="25">
         <f>'OPEX DATA 2'!U250</f>
-        <v>506.42788461538458</v>
+        <v>434.08104395604397</v>
       </c>
       <c r="E139" s="13">
         <f t="shared" si="5"/>
-        <v>1.5752033736092833E-3</v>
+        <v>1.3501743202365287E-3</v>
       </c>
     </row>
     <row r="140" spans="2:7" x14ac:dyDescent="0.25">
@@ -9731,11 +9731,11 @@
       <c r="C141" s="36"/>
       <c r="D141" s="37">
         <f>SUM(D133:D140)</f>
-        <v>1498.2273717948717</v>
+        <v>1284.1948901098901</v>
       </c>
       <c r="E141" s="38">
         <f t="shared" si="5"/>
-        <v>4.6601162419747178E-3</v>
+        <v>3.9943853502640439E-3</v>
       </c>
       <c r="F141" s="38"/>
       <c r="G141" s="38"/>
@@ -9778,11 +9778,11 @@
       <c r="C145" s="44"/>
       <c r="D145" s="45">
         <f>'OPEX DATA 2'!U256</f>
-        <v>6814.9904487179483</v>
+        <v>5841.4203846153841</v>
       </c>
       <c r="E145" s="46">
         <f t="shared" si="6"/>
-        <v>2.1197481955576823E-2</v>
+        <v>1.8169270247637277E-2</v>
       </c>
     </row>
     <row r="146" spans="2:7" x14ac:dyDescent="0.25">
@@ -9808,11 +9808,11 @@
       <c r="C147" s="44"/>
       <c r="D147" s="45">
         <f>'OPEX DATA 2'!U258</f>
-        <v>764.69833333333338</v>
+        <v>655.45571428571441</v>
       </c>
       <c r="E147" s="46">
         <f t="shared" si="6"/>
-        <v>2.3785329186106793E-3</v>
+        <v>2.0387425016662967E-3</v>
       </c>
     </row>
     <row r="148" spans="2:7" x14ac:dyDescent="0.25">
@@ -9853,11 +9853,11 @@
       <c r="C150" s="44"/>
       <c r="D150" s="45">
         <f>'OPEX DATA 2'!U261</f>
-        <v>1483.8910256410256</v>
+        <v>1271.9065934065934</v>
       </c>
       <c r="E150" s="46">
         <f t="shared" si="6"/>
-        <v>4.6155241855086338E-3</v>
+        <v>3.9561635875788289E-3</v>
       </c>
     </row>
     <row r="151" spans="2:7" x14ac:dyDescent="0.25">
@@ -9868,11 +9868,11 @@
       <c r="C151" s="44"/>
       <c r="D151" s="45">
         <f>'OPEX DATA 2'!U262</f>
-        <v>124.16967948717949</v>
+        <v>106.43115384615385</v>
       </c>
       <c r="E151" s="46">
         <f t="shared" si="6"/>
-        <v>3.8621984288391754E-4</v>
+        <v>3.3104557961478648E-4</v>
       </c>
     </row>
     <row r="152" spans="2:7" x14ac:dyDescent="0.25">
@@ -9944,11 +9944,11 @@
       <c r="C157" s="44"/>
       <c r="D157" s="45">
         <f>'OPEX DATA 2'!U268</f>
-        <v>-455.96987179487178</v>
+        <v>-390.83131868131869</v>
       </c>
       <c r="E157" s="46">
         <f t="shared" si="7"/>
-        <v>-1.4182577660804721E-3</v>
+        <v>-1.2156495137832619E-3</v>
       </c>
     </row>
     <row r="158" spans="2:7" x14ac:dyDescent="0.25">
@@ -10168,11 +10168,11 @@
       <c r="C172" s="36"/>
       <c r="D172" s="37">
         <f>SUM(D155:D171)</f>
-        <v>-11065.469871794872</v>
+        <v>-11000.331318681319</v>
       </c>
       <c r="E172" s="38">
         <f t="shared" si="7"/>
-        <v>-3.4418257766080471E-2</v>
+        <v>-3.4215649513783267E-2</v>
       </c>
       <c r="F172" s="38"/>
       <c r="G172" s="38"/>
@@ -10215,11 +10215,11 @@
       <c r="C176" s="44"/>
       <c r="D176" s="45">
         <f>'OPEX DATA 2'!U289</f>
-        <v>673.88282051282056</v>
+        <v>577.61384615384611</v>
       </c>
       <c r="E176" s="46">
         <f t="shared" si="8"/>
-        <v>2.096058539697731E-3</v>
+        <v>1.7966216054551979E-3</v>
       </c>
     </row>
     <row r="177" spans="2:5" x14ac:dyDescent="0.25">
@@ -10230,11 +10230,11 @@
       <c r="C177" s="44"/>
       <c r="D177" s="45">
         <f>'OPEX DATA 2'!U290</f>
-        <v>7274.7650641025648</v>
+        <v>6235.5129120879128</v>
       </c>
       <c r="E177" s="46">
         <f t="shared" si="8"/>
-        <v>2.2627574071858676E-2</v>
+        <v>1.939506349016458E-2</v>
       </c>
     </row>
     <row r="178" spans="2:5" x14ac:dyDescent="0.25">
@@ -10245,11 +10245,11 @@
       <c r="C178" s="44"/>
       <c r="D178" s="45">
         <f>'OPEX DATA 2'!U291</f>
-        <v>3.5256410256410255</v>
+        <v>3.0219780219780219</v>
       </c>
       <c r="E178" s="46">
         <f t="shared" si="8"/>
-        <v>1.0966224029987637E-5</v>
+        <v>9.3996205971322615E-6</v>
       </c>
     </row>
     <row r="179" spans="2:5" x14ac:dyDescent="0.25">
@@ -10260,11 +10260,11 @@
       <c r="C179" s="44"/>
       <c r="D179" s="45">
         <f>'OPEX DATA 2'!U292</f>
-        <v>104.23096153846154</v>
+        <v>89.340824175824181</v>
       </c>
       <c r="E179" s="46">
         <f t="shared" si="8"/>
-        <v>3.2420205766239981E-4</v>
+        <v>2.7788747799634269E-4</v>
       </c>
     </row>
     <row r="180" spans="2:5" x14ac:dyDescent="0.25">
@@ -10275,11 +10275,11 @@
       <c r="C180" s="44"/>
       <c r="D180" s="45">
         <f>'OPEX DATA 2'!U293</f>
-        <v>33.975576923076922</v>
+        <v>29.121923076923078</v>
       </c>
       <c r="E180" s="46">
         <f t="shared" si="8"/>
-        <v>1.0567831080272759E-4</v>
+        <v>9.0581409259480803E-5</v>
       </c>
     </row>
     <row r="181" spans="2:5" x14ac:dyDescent="0.25">
@@ -10290,11 +10290,11 @@
       <c r="C181" s="44"/>
       <c r="D181" s="45">
         <f>'OPEX DATA 2'!U294</f>
-        <v>562.1480128205128</v>
+        <v>481.84115384615382</v>
       </c>
       <c r="E181" s="46">
         <f t="shared" si="8"/>
-        <v>1.7485163695816883E-3</v>
+        <v>1.4987283167843043E-3</v>
       </c>
     </row>
     <row r="182" spans="2:5" x14ac:dyDescent="0.25">
@@ -10305,11 +10305,11 @@
       <c r="C182" s="44"/>
       <c r="D182" s="45">
         <f>'OPEX DATA 2'!U295</f>
-        <v>39.474423076923081</v>
+        <v>33.835219780219781</v>
       </c>
       <c r="E182" s="46">
         <f t="shared" si="8"/>
-        <v>1.2278203134346216E-4</v>
+        <v>1.0524174115153898E-4</v>
       </c>
     </row>
     <row r="183" spans="2:5" x14ac:dyDescent="0.25">
@@ -10335,11 +10335,11 @@
       <c r="C184" s="44"/>
       <c r="D184" s="45">
         <f>'OPEX DATA 2'!U297</f>
-        <v>17.186666666666664</v>
+        <v>14.73142857142857</v>
       </c>
       <c r="E184" s="46">
         <f t="shared" si="8"/>
-        <v>5.3457750129600823E-5</v>
+        <v>4.5820928682514988E-5</v>
       </c>
     </row>
     <row r="185" spans="2:5" x14ac:dyDescent="0.25">
@@ -10545,11 +10545,11 @@
       <c r="C198" s="44"/>
       <c r="D198" s="45">
         <f>'OPEX DATA 2'!U311</f>
-        <v>35.71294871794872</v>
+        <v>30.611098901098902</v>
       </c>
       <c r="E198" s="46">
         <f t="shared" si="8"/>
-        <v>1.1108226661881405E-4</v>
+        <v>9.5213371387554903E-5</v>
       </c>
     </row>
     <row r="199" spans="2:175" x14ac:dyDescent="0.25">
@@ -10590,11 +10590,11 @@
       <c r="C201" s="36"/>
       <c r="D201" s="37">
         <f>SUM(D175:D200)</f>
-        <v>8744.9021153846134</v>
+        <v>7495.6303846153842</v>
       </c>
       <c r="E201" s="38">
         <f t="shared" si="8"/>
-        <v>2.7200317621725079E-2</v>
+        <v>2.3314557961478643E-2</v>
       </c>
       <c r="F201" s="38"/>
       <c r="G201" s="38"/>
@@ -10612,21 +10612,21 @@
       <c r="C203" s="36"/>
       <c r="D203" s="37">
         <f>D43-D50-D101-D130-D141-D152-D172-D201</f>
-        <v>80452.437628205123</v>
+        <v>84353.867536629987</v>
       </c>
       <c r="E203" s="38">
         <f>D203/D36</f>
-        <v>0.2502408635402959</v>
+        <v>0.26237594879200615</v>
       </c>
       <c r="F203" s="38"/>
       <c r="G203" s="38"/>
     </row>
     <row r="205" spans="2:175" x14ac:dyDescent="0.25">
-      <c r="D205" s="79">
+      <c r="D205" s="84">
         <f>D2</f>
         <v>46025</v>
       </c>
-      <c r="E205" s="79"/>
+      <c r="E205" s="84"/>
     </row>
     <row r="206" spans="2:175" x14ac:dyDescent="0.25">
       <c r="B206" s="8" t="s">
@@ -10642,7 +10642,7 @@
       <c r="C207" s="50"/>
       <c r="D207" s="51">
         <f>E203</f>
-        <v>0.2502408635402959</v>
+        <v>0.26237594879200615</v>
       </c>
     </row>
     <row r="208" spans="2:175" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -18344,12 +18344,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D8:E8"/>
     <mergeCell ref="D205:E205"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="D11:E11"/>
@@ -18357,6 +18351,12 @@
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D8:E8"/>
   </mergeCells>
   <conditionalFormatting sqref="D30">
     <cfRule type="cellIs" dxfId="1" priority="1" stopIfTrue="1" operator="lessThan">
@@ -18393,6 +18393,7 @@
     <col min="16" max="16" width="1.25" customWidth="1"/>
     <col min="17" max="17" width="15" customWidth="1"/>
     <col min="18" max="18" width="8.25" customWidth="1"/>
+    <col min="20" max="20" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
@@ -18410,55 +18411,55 @@
       <c r="A5" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="90" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="78" t="s">
+      <c r="C5" s="91" t="s">
         <v>31</v>
       </c>
       <c r="D5" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="77" t="s">
+      <c r="E5" s="90" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="78" t="s">
+      <c r="F5" s="91" t="s">
         <v>31</v>
       </c>
       <c r="G5" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="77" t="s">
+      <c r="H5" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="78" t="s">
+      <c r="I5" s="91" t="s">
         <v>31</v>
       </c>
       <c r="J5" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="K5" s="77" t="s">
+      <c r="K5" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="L5" s="78" t="s">
+      <c r="L5" s="91" t="s">
         <v>31</v>
       </c>
       <c r="M5" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="N5" s="77" t="s">
+      <c r="N5" s="90" t="s">
         <v>36</v>
       </c>
-      <c r="O5" s="78" t="s">
+      <c r="O5" s="91" t="s">
         <v>31</v>
       </c>
       <c r="P5" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="Q5" s="77" t="s">
+      <c r="Q5" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="R5" s="78" t="s">
+      <c r="R5" s="91" t="s">
         <v>31</v>
       </c>
       <c r="T5" s="55" t="s">
@@ -18568,8 +18569,8 @@
         <v>8906790.2200000007</v>
       </c>
       <c r="U8" s="65">
-        <f>(T8/$V$1)/6</f>
-        <v>57094.809102564112</v>
+        <f>(T8/$V$1)/7</f>
+        <v>48938.407802197806</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
@@ -18628,7 +18629,7 @@
         <v>0</v>
       </c>
       <c r="U9" s="65">
-        <f t="shared" ref="U9:U72" si="1">(T9/$V$1)/6</f>
+        <f t="shared" ref="U9:U72" si="1">(T9/$V$1)/7</f>
         <v>0</v>
       </c>
     </row>
@@ -18695,7 +18696,7 @@
       </c>
       <c r="U10" s="65">
         <f t="shared" si="1"/>
-        <v>57094.809102564112</v>
+        <v>48938.407802197806</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
@@ -18755,7 +18756,7 @@
       </c>
       <c r="U11" s="65">
         <f t="shared" si="1"/>
-        <v>5410.3425641025633</v>
+        <v>4637.4364835164833</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
@@ -18905,7 +18906,7 @@
       </c>
       <c r="U14" s="65">
         <f t="shared" si="1"/>
-        <v>55620.65621794873</v>
+        <v>47674.848186813193</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
@@ -18965,7 +18966,7 @@
       </c>
       <c r="U15" s="65">
         <f t="shared" si="1"/>
-        <v>649.05769230769226</v>
+        <v>556.33516483516485</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
@@ -19025,7 +19026,7 @@
       </c>
       <c r="U16" s="65">
         <f t="shared" si="1"/>
-        <v>18386.820705128208</v>
+        <v>15760.132032967036</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
@@ -19085,7 +19086,7 @@
       </c>
       <c r="U17" s="65">
         <f t="shared" si="1"/>
-        <v>3318.8911538461539</v>
+        <v>2844.7638461538459</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -19211,7 +19212,7 @@
       </c>
       <c r="U19" s="65">
         <f t="shared" si="1"/>
-        <v>77975.425769230773</v>
+        <v>66836.079230769232</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -19361,7 +19362,7 @@
       </c>
       <c r="U22" s="65">
         <f t="shared" si="1"/>
-        <v>2213.1826923076924</v>
+        <v>1897.0137362637363</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -19421,7 +19422,7 @@
       </c>
       <c r="U23" s="65">
         <f t="shared" si="1"/>
-        <v>366.48724358974363</v>
+        <v>314.1319230769231</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -19541,7 +19542,7 @@
       </c>
       <c r="U25" s="65">
         <f t="shared" si="1"/>
-        <v>391.39474358974365</v>
+        <v>335.48120879120881</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -19601,7 +19602,7 @@
       </c>
       <c r="U26" s="65">
         <f t="shared" si="1"/>
-        <v>2047.7985256410257</v>
+        <v>1755.2558791208792</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -19847,7 +19848,7 @@
       </c>
       <c r="U30" s="65">
         <f t="shared" si="1"/>
-        <v>5018.8632051282048</v>
+        <v>4301.8827472527473</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -20393,7 +20394,7 @@
       </c>
       <c r="U40" s="65">
         <f t="shared" si="1"/>
-        <v>-23.881410256410259</v>
+        <v>-20.469780219780223</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -20453,7 +20454,7 @@
       </c>
       <c r="U41" s="65">
         <f t="shared" si="1"/>
-        <v>-257.87820512820514</v>
+        <v>-221.03846153846152</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -20513,7 +20514,7 @@
       </c>
       <c r="U42" s="65">
         <f t="shared" si="1"/>
-        <v>-508.08173076923077</v>
+        <v>-435.49862637362639</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -20573,7 +20574,7 @@
       </c>
       <c r="U43" s="65">
         <f t="shared" si="1"/>
-        <v>-799.84615384615381</v>
+        <v>-685.58241758241752</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -20633,7 +20634,7 @@
       </c>
       <c r="U44" s="65">
         <f t="shared" si="1"/>
-        <v>-52.974358974358978</v>
+        <v>-45.406593406593409</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -20753,7 +20754,7 @@
       </c>
       <c r="U46" s="65">
         <f t="shared" si="1"/>
-        <v>-1207.25</v>
+        <v>-1034.7857142857142</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -20813,7 +20814,7 @@
       </c>
       <c r="U47" s="65">
         <f t="shared" si="1"/>
-        <v>-1073.3971153846155</v>
+        <v>-920.05467032967044</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -20873,7 +20874,7 @@
       </c>
       <c r="U48" s="65">
         <f t="shared" si="1"/>
-        <v>-318.72435897435895</v>
+        <v>-273.19230769230768</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -20993,7 +20994,7 @@
       </c>
       <c r="U50" s="65">
         <f t="shared" si="1"/>
-        <v>-404.76923076923077</v>
+        <v>-346.94505494505495</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -21059,7 +21060,7 @@
       </c>
       <c r="U51" s="65">
         <f t="shared" si="1"/>
-        <v>-4646.8025641025642</v>
+        <v>-3982.9736263736268</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -21125,7 +21126,7 @@
       </c>
       <c r="U52" s="65">
         <f t="shared" si="1"/>
-        <v>140852.63807692306</v>
+        <v>120730.83263736263</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -21305,7 +21306,7 @@
       </c>
       <c r="U56" s="65">
         <f t="shared" si="1"/>
-        <v>2599.1747435897432</v>
+        <v>2227.8640659340658</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -21365,7 +21366,7 @@
       </c>
       <c r="U57" s="65">
         <f t="shared" si="1"/>
-        <v>802.11256410256408</v>
+        <v>687.52505494505488</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -21425,7 +21426,7 @@
       </c>
       <c r="U58" s="65">
         <f t="shared" si="1"/>
-        <v>3103.853012820513</v>
+        <v>2660.4454395604398</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -21485,7 +21486,7 @@
       </c>
       <c r="U59" s="65">
         <f t="shared" si="1"/>
-        <v>253.56525641025647</v>
+        <v>217.34164835164842</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -21545,7 +21546,7 @@
       </c>
       <c r="U60" s="65">
         <f t="shared" si="1"/>
-        <v>5168.6726282051277</v>
+        <v>4430.2908241758241</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -21605,7 +21606,7 @@
       </c>
       <c r="U61" s="65">
         <f t="shared" si="1"/>
-        <v>2242.9720512820513</v>
+        <v>1922.5474725274726</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -21665,7 +21666,7 @@
       </c>
       <c r="U62" s="65">
         <f t="shared" si="1"/>
-        <v>364.98685897435894</v>
+        <v>312.84587912087909</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -21725,7 +21726,7 @@
       </c>
       <c r="U63" s="65">
         <f t="shared" si="1"/>
-        <v>509.31410256410254</v>
+        <v>436.55494505494505</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -21851,7 +21852,7 @@
       </c>
       <c r="U65" s="65">
         <f t="shared" si="1"/>
-        <v>15044.65121794872</v>
+        <v>12895.415329670332</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -21911,7 +21912,7 @@
       </c>
       <c r="U66" s="65">
         <f t="shared" si="1"/>
-        <v>1148.9414743589743</v>
+        <v>984.8069780219779</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -22061,7 +22062,7 @@
       </c>
       <c r="U69" s="65">
         <f t="shared" si="1"/>
-        <v>86.683141025641021</v>
+        <v>74.299835164835159</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -22121,7 +22122,7 @@
       </c>
       <c r="U70" s="65">
         <f t="shared" si="1"/>
-        <v>1791.7158333333334</v>
+        <v>1535.7564285714286</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -22181,7 +22182,7 @@
       </c>
       <c r="U71" s="65">
         <f t="shared" si="1"/>
-        <v>2031.2403846153848</v>
+        <v>1741.063186813187</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -22241,7 +22242,7 @@
       </c>
       <c r="U72" s="65">
         <f t="shared" si="1"/>
-        <v>334.995</v>
+        <v>287.13857142857142</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -22300,8 +22301,8 @@
         <v>749037.25</v>
       </c>
       <c r="U73" s="65">
-        <f t="shared" ref="U73:U136" si="3">(T73/$V$1)/6</f>
-        <v>4801.520833333333</v>
+        <f t="shared" ref="U73:U136" si="3">(T73/$V$1)/7</f>
+        <v>4115.5892857142853</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -22361,7 +22362,7 @@
       </c>
       <c r="U74" s="65">
         <f t="shared" si="3"/>
-        <v>803.17570512820521</v>
+        <v>688.43631868131877</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -22421,7 +22422,7 @@
       </c>
       <c r="U75" s="65">
         <f t="shared" si="3"/>
-        <v>459.47134615384613</v>
+        <v>393.83258241758239</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -22487,7 +22488,7 @@
       </c>
       <c r="U76" s="65">
         <f t="shared" si="3"/>
-        <v>10308.802243589746</v>
+        <v>8836.1162087912107</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -22942,7 +22943,7 @@
         <v>740515.92999999993</v>
       </c>
       <c r="U85" s="65">
-        <f t="shared" si="3"/>
+        <f>(T85/$V$1)/6</f>
         <v>4746.896987179487</v>
       </c>
     </row>
@@ -23002,7 +23003,7 @@
         <v>234539.99000000002</v>
       </c>
       <c r="U86" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="U86:U149" si="4">(T86/$V$1)/6</f>
         <v>1503.4614743589746</v>
       </c>
     </row>
@@ -23062,7 +23063,7 @@
         <v>123804.48</v>
       </c>
       <c r="U87" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>793.61846153846147</v>
       </c>
     </row>
@@ -23122,7 +23123,7 @@
         <v>176434.82</v>
       </c>
       <c r="U88" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1130.9924358974361</v>
       </c>
     </row>
@@ -23182,7 +23183,7 @@
         <v>219374.05999999997</v>
       </c>
       <c r="U89" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1406.2439743589741</v>
       </c>
     </row>
@@ -23242,7 +23243,7 @@
         <v>49639.69</v>
       </c>
       <c r="U90" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>318.20314102564106</v>
       </c>
     </row>
@@ -23302,7 +23303,7 @@
         <v>23569.62</v>
       </c>
       <c r="U91" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>151.08730769230769</v>
       </c>
     </row>
@@ -23362,7 +23363,7 @@
         <v>301450.84999999998</v>
       </c>
       <c r="U92" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1932.3772435897436</v>
       </c>
     </row>
@@ -23422,7 +23423,7 @@
         <v>74921.850000000006</v>
       </c>
       <c r="U93" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>480.26826923076925</v>
       </c>
     </row>
@@ -23482,7 +23483,7 @@
         <v>53241.24</v>
       </c>
       <c r="U94" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>341.29</v>
       </c>
     </row>
@@ -23542,7 +23543,7 @@
         <v>0</v>
       </c>
       <c r="U95" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -23602,7 +23603,7 @@
         <v>36115</v>
       </c>
       <c r="U96" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>231.50641025641025</v>
       </c>
     </row>
@@ -23662,7 +23663,7 @@
         <v>166209.85999999999</v>
       </c>
       <c r="U97" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1065.4478205128205</v>
       </c>
     </row>
@@ -23722,7 +23723,7 @@
         <v>68883.759999999995</v>
       </c>
       <c r="U98" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>441.56256410256407</v>
       </c>
     </row>
@@ -23782,7 +23783,7 @@
         <v>0</v>
       </c>
       <c r="U99" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -23842,7 +23843,7 @@
         <v>0</v>
       </c>
       <c r="U100" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -23902,7 +23903,7 @@
         <v>0</v>
       </c>
       <c r="U101" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -23962,7 +23963,7 @@
         <v>0</v>
       </c>
       <c r="U102" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -24022,7 +24023,7 @@
         <v>0</v>
       </c>
       <c r="U103" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -24082,7 +24083,7 @@
         <v>0</v>
       </c>
       <c r="U104" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -24142,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="U105" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -24202,7 +24203,7 @@
         <v>0</v>
       </c>
       <c r="U106" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -24262,7 +24263,7 @@
         <v>5348.869999999999</v>
       </c>
       <c r="U107" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>34.2876282051282</v>
       </c>
     </row>
@@ -24322,7 +24323,7 @@
         <v>0</v>
       </c>
       <c r="U108" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -24382,7 +24383,7 @@
         <v>0</v>
       </c>
       <c r="U109" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -24442,7 +24443,7 @@
         <v>86116.89</v>
       </c>
       <c r="U110" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>552.03134615384613</v>
       </c>
     </row>
@@ -24502,7 +24503,7 @@
         <v>45686.84</v>
       </c>
       <c r="U111" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>292.86435897435894</v>
       </c>
     </row>
@@ -24562,7 +24563,7 @@
         <v>75558.930000000008</v>
       </c>
       <c r="U112" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>484.35211538461544</v>
       </c>
     </row>
@@ -24622,7 +24623,7 @@
         <v>0</v>
       </c>
       <c r="U113" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -24682,7 +24683,7 @@
         <v>23663.919999999998</v>
       </c>
       <c r="U114" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>151.69179487179485</v>
       </c>
     </row>
@@ -24742,7 +24743,7 @@
         <v>0</v>
       </c>
       <c r="U115" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -24802,7 +24803,7 @@
         <v>24894.87</v>
       </c>
       <c r="U116" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>159.58250000000001</v>
       </c>
     </row>
@@ -24862,7 +24863,7 @@
         <v>0</v>
       </c>
       <c r="U117" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -24922,7 +24923,7 @@
         <v>46105.82</v>
       </c>
       <c r="U118" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>295.5501282051282</v>
       </c>
     </row>
@@ -24988,7 +24989,7 @@
         <v>2576077.2899999996</v>
       </c>
       <c r="U119" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>16513.315961538461</v>
       </c>
     </row>
@@ -25054,7 +25055,7 @@
         <v>2576077.2899999996</v>
       </c>
       <c r="U120" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>16513.315961538461</v>
       </c>
     </row>
@@ -25084,7 +25085,7 @@
         <v>0</v>
       </c>
       <c r="U121" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -25144,7 +25145,7 @@
         <v>0</v>
       </c>
       <c r="U122" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -25204,7 +25205,7 @@
         <v>178783.79</v>
       </c>
       <c r="U123" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1146.0499358974359</v>
       </c>
     </row>
@@ -25264,7 +25265,7 @@
         <v>381615.75000000006</v>
       </c>
       <c r="U124" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2446.2548076923081</v>
       </c>
     </row>
@@ -25324,7 +25325,7 @@
         <v>0</v>
       </c>
       <c r="U125" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -25384,7 +25385,7 @@
         <v>0</v>
       </c>
       <c r="U126" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -25444,7 +25445,7 @@
         <v>0</v>
       </c>
       <c r="U127" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -25504,7 +25505,7 @@
         <v>0</v>
       </c>
       <c r="U128" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -25564,7 +25565,7 @@
         <v>0</v>
       </c>
       <c r="U129" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -25624,7 +25625,7 @@
         <v>20144.52</v>
       </c>
       <c r="U130" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>129.13153846153847</v>
       </c>
     </row>
@@ -25684,7 +25685,7 @@
         <v>0</v>
       </c>
       <c r="U131" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -25744,7 +25745,7 @@
         <v>0</v>
       </c>
       <c r="U132" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -25804,7 +25805,7 @@
         <v>0</v>
       </c>
       <c r="U133" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -25864,7 +25865,7 @@
         <v>0</v>
       </c>
       <c r="U134" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -25924,7 +25925,7 @@
         <v>0</v>
       </c>
       <c r="U135" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -25984,7 +25985,7 @@
         <v>0</v>
       </c>
       <c r="U136" s="65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -26040,11 +26041,11 @@
         <v>0</v>
       </c>
       <c r="T137" s="65">
-        <f t="shared" ref="T137:T200" si="4">IFERROR(B137+E137+H137+K137+N137+Q137, "NA")</f>
+        <f t="shared" ref="T137:T200" si="5">IFERROR(B137+E137+H137+K137+N137+Q137, "NA")</f>
         <v>0</v>
       </c>
       <c r="U137" s="65">
-        <f t="shared" ref="U137:U200" si="5">(T137/$V$1)/6</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -26100,11 +26101,11 @@
         <v>0</v>
       </c>
       <c r="T138" s="65">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U138" s="65">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U138" s="65">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -26160,11 +26161,11 @@
         <v>4.2175475524910008E-2</v>
       </c>
       <c r="T139" s="65">
+        <f t="shared" si="5"/>
+        <v>823250.07000000007</v>
+      </c>
+      <c r="U139" s="65">
         <f t="shared" si="4"/>
-        <v>823250.07000000007</v>
-      </c>
-      <c r="U139" s="65">
-        <f t="shared" si="5"/>
         <v>5277.2440384615393</v>
       </c>
     </row>
@@ -26220,11 +26221,11 @@
         <v>0</v>
       </c>
       <c r="T140" s="65">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U140" s="65">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U140" s="65">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -26280,11 +26281,11 @@
         <v>1.4841958591579944E-2</v>
       </c>
       <c r="T141" s="65">
+        <f t="shared" si="5"/>
+        <v>241357.00999999998</v>
+      </c>
+      <c r="U141" s="65">
         <f t="shared" si="4"/>
-        <v>241357.00999999998</v>
-      </c>
-      <c r="U141" s="65">
-        <f t="shared" si="5"/>
         <v>1547.1603205128204</v>
       </c>
     </row>
@@ -26340,11 +26341,11 @@
         <v>7.2850673814841135E-3</v>
       </c>
       <c r="T142" s="65">
+        <f t="shared" si="5"/>
+        <v>153282.78</v>
+      </c>
+      <c r="U142" s="65">
         <f t="shared" si="4"/>
-        <v>153282.78</v>
-      </c>
-      <c r="U142" s="65">
-        <f t="shared" si="5"/>
         <v>982.58192307692309</v>
       </c>
     </row>
@@ -26406,11 +26407,11 @@
         <v>9.1371804215976682E-2</v>
       </c>
       <c r="T143" s="65">
+        <f t="shared" si="5"/>
+        <v>1798433.9200000002</v>
+      </c>
+      <c r="U143" s="65">
         <f t="shared" si="4"/>
-        <v>1798433.9200000002</v>
-      </c>
-      <c r="U143" s="65">
-        <f t="shared" si="5"/>
         <v>11528.422564102564</v>
       </c>
     </row>
@@ -26436,11 +26437,11 @@
       <c r="Q144" s="57"/>
       <c r="R144" s="58"/>
       <c r="T144" s="65">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U144" s="65">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U144" s="65">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -26496,11 +26497,11 @@
         <v>0</v>
       </c>
       <c r="T145" s="65">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U145" s="65">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U145" s="65">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -26556,11 +26557,11 @@
         <v>2.6463670129150147E-2</v>
       </c>
       <c r="T146" s="65">
+        <f t="shared" si="5"/>
+        <v>523648.92</v>
+      </c>
+      <c r="U146" s="65">
         <f t="shared" si="4"/>
-        <v>523648.92</v>
-      </c>
-      <c r="U146" s="65">
-        <f t="shared" si="5"/>
         <v>3356.7238461538459</v>
       </c>
     </row>
@@ -26616,11 +26617,11 @@
         <v>-2.9908564926949999E-3</v>
       </c>
       <c r="T147" s="65">
+        <f t="shared" si="5"/>
+        <v>43518.020000000004</v>
+      </c>
+      <c r="U147" s="65">
         <f t="shared" si="4"/>
-        <v>43518.020000000004</v>
-      </c>
-      <c r="U147" s="65">
-        <f t="shared" si="5"/>
         <v>278.9616666666667</v>
       </c>
     </row>
@@ -26676,11 +26677,11 @@
         <v>2.4906680521712744E-3</v>
       </c>
       <c r="T148" s="65">
+        <f t="shared" si="5"/>
+        <v>66941.05</v>
+      </c>
+      <c r="U148" s="65">
         <f t="shared" si="4"/>
-        <v>66941.05</v>
-      </c>
-      <c r="U148" s="65">
-        <f t="shared" si="5"/>
         <v>429.10929487179487</v>
       </c>
     </row>
@@ -26736,11 +26737,11 @@
         <v>7.2087865777490196E-3</v>
       </c>
       <c r="T149" s="65">
+        <f t="shared" si="5"/>
+        <v>64484.270000000004</v>
+      </c>
+      <c r="U149" s="65">
         <f t="shared" si="4"/>
-        <v>64484.270000000004</v>
-      </c>
-      <c r="U149" s="65">
-        <f t="shared" si="5"/>
         <v>413.36070512820515</v>
       </c>
     </row>
@@ -26796,11 +26797,11 @@
         <v>2.2833236778792309E-3</v>
       </c>
       <c r="T150" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>66254.599999999991</v>
       </c>
       <c r="U150" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="U150:U157" si="6">(T150/$V$1)/6</f>
         <v>424.70897435897427</v>
       </c>
     </row>
@@ -26862,11 +26863,11 @@
         <v>3.5455591944254676E-2</v>
       </c>
       <c r="T151" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>764846.86</v>
       </c>
       <c r="U151" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4902.8644871794868</v>
       </c>
     </row>
@@ -26922,11 +26923,11 @@
         <v>0</v>
       </c>
       <c r="T152" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U152" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -26982,11 +26983,11 @@
         <v>5.0284301132119342E-3</v>
       </c>
       <c r="T153" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>83514.94</v>
       </c>
       <c r="U153" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>535.35217948717957</v>
       </c>
     </row>
@@ -27042,11 +27043,11 @@
         <v>2.8652421791085583E-4</v>
       </c>
       <c r="T154" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4442.3500000000004</v>
       </c>
       <c r="U154" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>28.476602564102567</v>
       </c>
     </row>
@@ -27102,11 +27103,11 @@
         <v>-3.8780887423252102E-5</v>
       </c>
       <c r="T155" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-472.95000000000005</v>
       </c>
       <c r="U155" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-3.0317307692307693</v>
       </c>
     </row>
@@ -27162,11 +27163,11 @@
         <v>1.1203367477828384E-5</v>
       </c>
       <c r="T156" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>146.01999999999998</v>
       </c>
       <c r="U156" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.9360256410256409</v>
       </c>
     </row>
@@ -27228,11 +27229,11 @@
         <v>0.47506724570703807</v>
       </c>
       <c r="T157" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9361362.040000001</v>
       </c>
       <c r="U157" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>60008.731025641027</v>
       </c>
     </row>
@@ -27258,11 +27259,11 @@
       <c r="Q158" s="57"/>
       <c r="R158" s="58"/>
       <c r="T158" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U158" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="U137:U200" si="7">(T158/$V$1)/7</f>
         <v>0</v>
       </c>
     </row>
@@ -27288,11 +27289,11 @@
       <c r="Q159" s="57"/>
       <c r="R159" s="58"/>
       <c r="T159" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U159" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -27348,11 +27349,11 @@
         <v>0</v>
       </c>
       <c r="T160" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U160" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -27408,12 +27409,12 @@
         <v>0</v>
       </c>
       <c r="T161" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.68</v>
       </c>
       <c r="U161" s="65">
-        <f t="shared" si="5"/>
-        <v>6.8461538461538463E-2</v>
+        <f t="shared" si="7"/>
+        <v>5.8681318681318685E-2</v>
       </c>
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
@@ -27468,12 +27469,12 @@
         <v>-1.550048326906923E-3</v>
       </c>
       <c r="T162" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>75637.47</v>
       </c>
       <c r="U162" s="65">
-        <f t="shared" si="5"/>
-        <v>484.85557692307697</v>
+        <f t="shared" si="7"/>
+        <v>415.59049450549452</v>
       </c>
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
@@ -27528,12 +27529,12 @@
         <v>1.0972411610853476E-3</v>
       </c>
       <c r="T163" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>71591.7</v>
       </c>
       <c r="U163" s="65">
-        <f t="shared" si="5"/>
-        <v>458.92115384615386</v>
+        <f t="shared" si="7"/>
+        <v>393.36098901098904</v>
       </c>
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
@@ -27588,12 +27589,12 @@
         <v>2.0980548034499617E-3</v>
       </c>
       <c r="T164" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6376.42</v>
       </c>
       <c r="U164" s="65">
-        <f t="shared" si="5"/>
-        <v>40.874487179487183</v>
+        <f t="shared" si="7"/>
+        <v>35.035274725274725</v>
       </c>
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
@@ -27648,12 +27649,12 @@
         <v>2.2797475113897094E-4</v>
       </c>
       <c r="T165" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9974.1</v>
       </c>
       <c r="U165" s="65">
-        <f t="shared" si="5"/>
-        <v>63.936538461538468</v>
+        <f t="shared" si="7"/>
+        <v>54.80274725274726</v>
       </c>
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
@@ -27708,12 +27709,12 @@
         <v>3.0664806888123452E-3</v>
       </c>
       <c r="T166" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>44206.920000000006</v>
       </c>
       <c r="U166" s="65">
-        <f t="shared" si="5"/>
-        <v>283.37769230769237</v>
+        <f t="shared" si="7"/>
+        <v>242.89516483516488</v>
       </c>
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
@@ -27768,12 +27769,12 @@
         <v>2.180098511544399E-3</v>
       </c>
       <c r="T167" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>40131.019999999997</v>
       </c>
       <c r="U167" s="65">
-        <f t="shared" si="5"/>
-        <v>257.25012820512819</v>
+        <f t="shared" si="7"/>
+        <v>220.50010989010985</v>
       </c>
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
@@ -27828,12 +27829,12 @@
         <v>5.6309526097321188E-3</v>
       </c>
       <c r="T168" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>90243.87</v>
       </c>
       <c r="U168" s="65">
-        <f t="shared" si="5"/>
-        <v>578.48634615384606</v>
+        <f t="shared" si="7"/>
+        <v>495.8454395604395</v>
       </c>
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
@@ -27888,12 +27889,12 @@
         <v>9.7265865946965309E-5</v>
       </c>
       <c r="T169" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8249.82</v>
       </c>
       <c r="U169" s="65">
-        <f t="shared" si="5"/>
-        <v>52.883461538461539</v>
+        <f t="shared" si="7"/>
+        <v>45.328681318681319</v>
       </c>
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
@@ -27948,12 +27949,12 @@
         <v>2.70826312663861E-3</v>
       </c>
       <c r="T170" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>85978.2</v>
       </c>
       <c r="U170" s="65">
-        <f t="shared" si="5"/>
-        <v>551.14230769230767</v>
+        <f t="shared" si="7"/>
+        <v>472.40769230769229</v>
       </c>
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
@@ -28008,12 +28009,12 @@
         <v>2.660966859172686E-3</v>
       </c>
       <c r="T171" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>75132.34</v>
       </c>
       <c r="U171" s="65">
-        <f t="shared" si="5"/>
-        <v>481.61756410256407</v>
+        <f t="shared" si="7"/>
+        <v>412.8150549450549</v>
       </c>
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
@@ -28068,11 +28069,11 @@
         <v>0</v>
       </c>
       <c r="T172" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U172" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -28128,12 +28129,12 @@
         <v>0</v>
       </c>
       <c r="T173" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>377.27</v>
       </c>
       <c r="U173" s="65">
-        <f t="shared" si="5"/>
-        <v>2.4183974358974356</v>
+        <f t="shared" si="7"/>
+        <v>2.0729120879120879</v>
       </c>
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
@@ -28188,12 +28189,12 @@
         <v>0</v>
       </c>
       <c r="T174" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4553.92</v>
       </c>
       <c r="U174" s="65">
-        <f t="shared" si="5"/>
-        <v>29.191794871794873</v>
+        <f t="shared" si="7"/>
+        <v>25.021538461538462</v>
       </c>
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
@@ -28248,12 +28249,12 @@
         <v>2.1402037361981812E-3</v>
       </c>
       <c r="T175" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>43440.729999999996</v>
       </c>
       <c r="U175" s="65">
-        <f t="shared" si="5"/>
-        <v>278.46621794871794</v>
+        <f t="shared" si="7"/>
+        <v>238.68532967032965</v>
       </c>
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
@@ -28308,12 +28309,12 @@
         <v>-1.2635651469721765E-3</v>
       </c>
       <c r="T176" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>33572.15</v>
       </c>
       <c r="U176" s="65">
-        <f t="shared" si="5"/>
-        <v>215.20608974358973</v>
+        <f t="shared" si="7"/>
+        <v>184.46236263736265</v>
       </c>
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
@@ -28368,12 +28369,12 @@
         <v>4.1309764762465099E-3</v>
       </c>
       <c r="T177" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>73153.279999999999</v>
       </c>
       <c r="U177" s="65">
-        <f t="shared" si="5"/>
-        <v>468.93128205128204</v>
+        <f t="shared" si="7"/>
+        <v>401.94109890109888</v>
       </c>
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
@@ -28428,12 +28429,12 @@
         <v>-4.1368918073742596E-4</v>
       </c>
       <c r="T178" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>82932.960000000006</v>
       </c>
       <c r="U178" s="65">
-        <f t="shared" si="5"/>
-        <v>531.62153846153853</v>
+        <f t="shared" si="7"/>
+        <v>455.67560439560441</v>
       </c>
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
@@ -28488,12 +28489,12 @@
         <v>1.0424671881155147E-3</v>
       </c>
       <c r="T179" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>35231.15</v>
       </c>
       <c r="U179" s="65">
-        <f t="shared" si="5"/>
-        <v>225.84070512820514</v>
+        <f t="shared" si="7"/>
+        <v>193.57774725274726</v>
       </c>
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
@@ -28548,12 +28549,12 @@
         <v>1.3428132895083707E-2</v>
       </c>
       <c r="T180" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>227647.32</v>
       </c>
       <c r="U180" s="65">
-        <f t="shared" si="5"/>
-        <v>1459.2776923076924</v>
+        <f t="shared" si="7"/>
+        <v>1250.8094505494505</v>
       </c>
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
@@ -28608,12 +28609,12 @@
         <v>0</v>
       </c>
       <c r="T181" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1000</v>
       </c>
       <c r="U181" s="65">
-        <f t="shared" si="5"/>
-        <v>6.4102564102564097</v>
+        <f t="shared" si="7"/>
+        <v>5.4945054945054945</v>
       </c>
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
@@ -28668,12 +28669,12 @@
         <v>1.0445337433410168E-4</v>
       </c>
       <c r="T182" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1472.04</v>
       </c>
       <c r="U182" s="65">
-        <f t="shared" si="5"/>
-        <v>9.4361538461538448</v>
+        <f t="shared" si="7"/>
+        <v>8.0881318681318675</v>
       </c>
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
@@ -28728,12 +28729,12 @@
         <v>2.4914213921612802E-3</v>
       </c>
       <c r="T183" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>44353.31</v>
       </c>
       <c r="U183" s="65">
-        <f t="shared" si="5"/>
-        <v>284.31608974358971</v>
+        <f t="shared" si="7"/>
+        <v>243.69950549450547</v>
       </c>
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
@@ -28788,12 +28789,12 @@
         <v>2.1173250645172681E-4</v>
       </c>
       <c r="T184" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4605.53</v>
       </c>
       <c r="U184" s="65">
-        <f t="shared" si="5"/>
-        <v>29.522628205128203</v>
+        <f t="shared" si="7"/>
+        <v>25.30510989010989</v>
       </c>
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
@@ -28848,12 +28849,12 @@
         <v>6.4574721049926831E-4</v>
       </c>
       <c r="T185" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9055.9500000000007</v>
       </c>
       <c r="U185" s="65">
-        <f t="shared" si="5"/>
-        <v>58.050961538461543</v>
+        <f t="shared" si="7"/>
+        <v>49.757967032967038</v>
       </c>
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
@@ -28908,11 +28909,11 @@
         <v>0</v>
       </c>
       <c r="T186" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U186" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -28968,12 +28969,12 @@
         <v>9.9731075797528817E-4</v>
       </c>
       <c r="T187" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>25625.81</v>
       </c>
       <c r="U187" s="65">
-        <f t="shared" si="5"/>
-        <v>164.26801282051284</v>
+        <f t="shared" si="7"/>
+        <v>140.80115384615385</v>
       </c>
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
@@ -29028,12 +29029,12 @@
         <v>1.8211920976288294E-3</v>
       </c>
       <c r="T188" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>41028.269999999997</v>
       </c>
       <c r="U188" s="65">
-        <f t="shared" si="5"/>
-        <v>263.00173076923073</v>
+        <f t="shared" si="7"/>
+        <v>225.43005494505493</v>
       </c>
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
@@ -29088,12 +29089,12 @@
         <v>5.1448724391379552E-3</v>
       </c>
       <c r="T189" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>127409.93</v>
       </c>
       <c r="U189" s="65">
-        <f t="shared" si="5"/>
-        <v>816.73032051282053</v>
+        <f t="shared" si="7"/>
+        <v>700.05456043956042</v>
       </c>
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
@@ -29148,12 +29149,12 @@
         <v>0</v>
       </c>
       <c r="T190" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7242.63</v>
       </c>
       <c r="U190" s="65">
-        <f t="shared" si="5"/>
-        <v>46.427115384615384</v>
+        <f t="shared" si="7"/>
+        <v>39.794670329670332</v>
       </c>
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
@@ -29208,11 +29209,11 @@
         <v>0</v>
       </c>
       <c r="T191" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U191" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -29268,12 +29269,12 @@
         <v>2.9869256408405344E-3</v>
       </c>
       <c r="T192" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>52286.77</v>
       </c>
       <c r="U192" s="65">
-        <f t="shared" si="5"/>
-        <v>335.17160256410256</v>
+        <f t="shared" si="7"/>
+        <v>287.28994505494501</v>
       </c>
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
@@ -29328,12 +29329,12 @@
         <v>1.4752613055022066E-2</v>
       </c>
       <c r="T193" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>257617.98</v>
       </c>
       <c r="U193" s="65">
-        <f t="shared" si="5"/>
-        <v>1651.3973076923078</v>
+        <f t="shared" si="7"/>
+        <v>1415.4834065934067</v>
       </c>
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
@@ -29388,12 +29389,12 @@
         <v>1.0330815098509258E-2</v>
       </c>
       <c r="T194" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>125372.71999999999</v>
       </c>
       <c r="U194" s="65">
-        <f t="shared" si="5"/>
-        <v>803.67128205128199</v>
+        <f t="shared" si="7"/>
+        <v>688.86109890109879</v>
       </c>
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
@@ -29448,12 +29449,12 @@
         <v>5.5934761436923398E-5</v>
       </c>
       <c r="T195" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10817.099999999999</v>
       </c>
       <c r="U195" s="65">
-        <f t="shared" si="5"/>
-        <v>69.340384615384608</v>
+        <f t="shared" si="7"/>
+        <v>59.434615384615377</v>
       </c>
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
@@ -29508,12 +29509,12 @@
         <v>4.8958387574301161E-2</v>
       </c>
       <c r="T196" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2291509.6999999997</v>
       </c>
       <c r="U196" s="65">
-        <f t="shared" si="5"/>
-        <v>14689.164743589741</v>
+        <f t="shared" si="7"/>
+        <v>12590.712637362636</v>
       </c>
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
@@ -29568,12 +29569,12 @@
         <v>0</v>
       </c>
       <c r="T197" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.13</v>
       </c>
       <c r="U197" s="65">
-        <f t="shared" si="5"/>
-        <v>1.3653846153846154E-2</v>
+        <f t="shared" si="7"/>
+        <v>1.1703296703296702E-2</v>
       </c>
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
@@ -29628,11 +29629,11 @@
         <v>0</v>
       </c>
       <c r="T198" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U198" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -29688,11 +29689,11 @@
         <v>0</v>
       </c>
       <c r="T199" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U199" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -29748,11 +29749,11 @@
         <v>0</v>
       </c>
       <c r="T200" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U200" s="65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -29808,12 +29809,12 @@
         <v>3.1494301636651945E-4</v>
       </c>
       <c r="T201" s="65">
-        <f t="shared" ref="T201:T264" si="6">IFERROR(B201+E201+H201+K201+N201+Q201, "NA")</f>
+        <f t="shared" ref="T201:T264" si="8">IFERROR(B201+E201+H201+K201+N201+Q201, "NA")</f>
         <v>9502.51</v>
       </c>
       <c r="U201" s="65">
-        <f t="shared" ref="U201:U264" si="7">(T201/$V$1)/6</f>
-        <v>60.913525641025643</v>
+        <f t="shared" ref="U201:U264" si="9">(T201/$V$1)/7</f>
+        <v>52.211593406593408</v>
       </c>
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
@@ -29868,11 +29869,11 @@
         <v>0</v>
       </c>
       <c r="T202" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U202" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -29928,11 +29929,11 @@
         <v>0</v>
       </c>
       <c r="T203" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U203" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -29988,11 +29989,11 @@
         <v>0</v>
       </c>
       <c r="T204" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U204" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -30048,11 +30049,11 @@
         <v>0</v>
       </c>
       <c r="T205" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U205" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -30108,11 +30109,11 @@
         <v>0</v>
       </c>
       <c r="T206" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U206" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -30168,11 +30169,11 @@
         <v>0</v>
       </c>
       <c r="T207" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U207" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -30228,11 +30229,11 @@
         <v>0</v>
       </c>
       <c r="T208" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U208" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -30294,12 +30295,12 @@
         <v>0.12609812494321374</v>
       </c>
       <c r="T209" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>4017343.7</v>
       </c>
       <c r="U209" s="65">
-        <f t="shared" si="7"/>
-        <v>25752.203205128204</v>
+        <f t="shared" si="9"/>
+        <v>22073.317032967032</v>
       </c>
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
@@ -30354,11 +30355,11 @@
         <v>0</v>
       </c>
       <c r="T210" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U210" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -30420,12 +30421,12 @@
         <v>0.12609812494321374</v>
       </c>
       <c r="T211" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>4017343.7</v>
       </c>
       <c r="U211" s="65">
-        <f t="shared" si="7"/>
-        <v>25752.203205128204</v>
+        <f t="shared" si="9"/>
+        <v>22073.317032967032</v>
       </c>
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
@@ -30450,11 +30451,11 @@
       <c r="Q212" s="57"/>
       <c r="R212" s="58"/>
       <c r="T212" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U212" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -30480,11 +30481,11 @@
       <c r="Q213" s="57"/>
       <c r="R213" s="58"/>
       <c r="T213" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U213" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -30540,11 +30541,11 @@
         <v>0</v>
       </c>
       <c r="T214" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U214" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -30600,12 +30601,12 @@
         <v>2.655615800216439E-2</v>
       </c>
       <c r="T215" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>566058.05999999994</v>
       </c>
       <c r="U215" s="65">
-        <f t="shared" si="7"/>
-        <v>3628.5773076923074</v>
+        <f t="shared" si="9"/>
+        <v>3110.2091208791207</v>
       </c>
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
@@ -30660,12 +30661,12 @@
         <v>-8.0903438615401199E-6</v>
       </c>
       <c r="T216" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>39374.769999999997</v>
       </c>
       <c r="U216" s="65">
-        <f t="shared" si="7"/>
-        <v>252.40237179487178</v>
+        <f t="shared" si="9"/>
+        <v>216.34489010989009</v>
       </c>
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
@@ -30720,12 +30721,12 @@
         <v>7.2164811982695061E-3</v>
       </c>
       <c r="T217" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>107413.67</v>
       </c>
       <c r="U217" s="65">
-        <f t="shared" si="7"/>
-        <v>688.54916666666668</v>
+        <f t="shared" si="9"/>
+        <v>590.18500000000006</v>
       </c>
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
@@ -30780,12 +30781,12 @@
         <v>1.4426871188370795E-3</v>
       </c>
       <c r="T218" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>34615.46</v>
       </c>
       <c r="U218" s="65">
-        <f t="shared" si="7"/>
-        <v>221.89397435897436</v>
+        <f t="shared" si="9"/>
+        <v>190.19483516483518</v>
       </c>
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
@@ -30840,12 +30841,12 @@
         <v>1.0890019079962109E-2</v>
       </c>
       <c r="T219" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>274906.38</v>
       </c>
       <c r="U219" s="65">
-        <f t="shared" si="7"/>
-        <v>1762.2203846153845</v>
+        <f t="shared" si="9"/>
+        <v>1510.4746153846154</v>
       </c>
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
@@ -30900,12 +30901,12 @@
         <v>-7.673222147229555E-5</v>
       </c>
       <c r="T220" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>600.56000000000029</v>
       </c>
       <c r="U220" s="65">
-        <f t="shared" si="7"/>
-        <v>3.8497435897435914</v>
+        <f t="shared" si="9"/>
+        <v>3.2997802197802213</v>
       </c>
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
@@ -30960,12 +30961,12 @@
         <v>3.3905546548631759E-3</v>
       </c>
       <c r="T221" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>52920.43</v>
       </c>
       <c r="U221" s="65">
-        <f t="shared" si="7"/>
-        <v>339.23352564102566</v>
+        <f t="shared" si="9"/>
+        <v>290.77159340659341</v>
       </c>
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
@@ -31020,12 +31021,12 @@
         <v>2.8972518004737822E-4</v>
       </c>
       <c r="T222" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>5819.6</v>
       </c>
       <c r="U222" s="65">
-        <f t="shared" si="7"/>
-        <v>37.305128205128206</v>
+        <f t="shared" si="9"/>
+        <v>31.975824175824179</v>
       </c>
     </row>
     <row r="223" spans="1:21" x14ac:dyDescent="0.25">
@@ -31080,12 +31081,12 @@
         <v>1.916414858622355E-4</v>
       </c>
       <c r="T223" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>4010.8500000000004</v>
       </c>
       <c r="U223" s="65">
-        <f t="shared" si="7"/>
-        <v>25.710576923076925</v>
+        <f t="shared" si="9"/>
+        <v>22.037637362637362</v>
       </c>
     </row>
     <row r="224" spans="1:21" x14ac:dyDescent="0.25">
@@ -31140,12 +31141,12 @@
         <v>-3.107161048272655E-7</v>
       </c>
       <c r="T224" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1146.9000000000001</v>
       </c>
       <c r="U224" s="65">
-        <f t="shared" si="7"/>
-        <v>7.3519230769230779</v>
+        <f t="shared" si="9"/>
+        <v>6.3016483516483524</v>
       </c>
     </row>
     <row r="225" spans="1:21" x14ac:dyDescent="0.25">
@@ -31200,12 +31201,12 @@
         <v>5.8853734051895004E-4</v>
       </c>
       <c r="T225" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2007.78</v>
       </c>
       <c r="U225" s="65">
-        <f t="shared" si="7"/>
-        <v>12.870384615384616</v>
+        <f t="shared" si="9"/>
+        <v>11.031758241758242</v>
       </c>
     </row>
     <row r="226" spans="1:21" x14ac:dyDescent="0.25">
@@ -31260,12 +31261,12 @@
         <v>2.8956689071095681E-4</v>
       </c>
       <c r="T226" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-24.300000000000068</v>
       </c>
       <c r="U226" s="65">
-        <f t="shared" si="7"/>
-        <v>-0.15576923076923122</v>
+        <f t="shared" si="9"/>
+        <v>-0.1335164835164839</v>
       </c>
     </row>
     <row r="227" spans="1:21" x14ac:dyDescent="0.25">
@@ -31320,12 +31321,12 @@
         <v>1.5766526605617559E-3</v>
       </c>
       <c r="T227" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>30953.070000000003</v>
       </c>
       <c r="U227" s="65">
-        <f t="shared" si="7"/>
-        <v>198.41711538461541</v>
+        <f t="shared" si="9"/>
+        <v>170.07181318681322</v>
       </c>
     </row>
     <row r="228" spans="1:21" x14ac:dyDescent="0.25">
@@ -31380,12 +31381,12 @@
         <v>2.5445303958146801E-4</v>
       </c>
       <c r="T228" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10715.01</v>
       </c>
       <c r="U228" s="65">
-        <f t="shared" si="7"/>
-        <v>68.685961538461541</v>
+        <f t="shared" si="9"/>
+        <v>58.873681318681314</v>
       </c>
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.25">
@@ -31440,12 +31441,12 @@
         <v>0</v>
       </c>
       <c r="T229" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>198</v>
       </c>
       <c r="U229" s="65">
-        <f t="shared" si="7"/>
-        <v>1.2692307692307692</v>
+        <f t="shared" si="9"/>
+        <v>1.0879120879120878</v>
       </c>
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.25">
@@ -31500,12 +31501,12 @@
         <v>2.5671452519348908E-3</v>
       </c>
       <c r="T230" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>44139.159999999996</v>
       </c>
       <c r="U230" s="65">
-        <f t="shared" si="7"/>
-        <v>282.94333333333333</v>
+        <f t="shared" si="9"/>
+        <v>242.52285714285713</v>
       </c>
     </row>
     <row r="231" spans="1:21" x14ac:dyDescent="0.25">
@@ -31560,11 +31561,11 @@
         <v>0</v>
       </c>
       <c r="T231" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U231" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -31620,12 +31621,12 @@
         <v>8.7938520234131745E-5</v>
       </c>
       <c r="T232" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>15800</v>
       </c>
       <c r="U232" s="65">
-        <f t="shared" si="7"/>
-        <v>101.28205128205128</v>
+        <f t="shared" si="9"/>
+        <v>86.813186813186817</v>
       </c>
     </row>
     <row r="233" spans="1:21" x14ac:dyDescent="0.25">
@@ -31680,12 +31681,12 @@
         <v>7.6046301014469329E-5</v>
       </c>
       <c r="T233" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>3268.84</v>
       </c>
       <c r="U233" s="65">
-        <f t="shared" si="7"/>
-        <v>20.954102564102566</v>
+        <f t="shared" si="9"/>
+        <v>17.96065934065934</v>
       </c>
     </row>
     <row r="234" spans="1:21" x14ac:dyDescent="0.25">
@@ -31740,12 +31741,12 @@
         <v>2.9869197782725186E-4</v>
       </c>
       <c r="T234" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>3534.63</v>
       </c>
       <c r="U234" s="65">
-        <f t="shared" si="7"/>
-        <v>22.657884615384617</v>
+        <f t="shared" si="9"/>
+        <v>19.421043956043956</v>
       </c>
     </row>
     <row r="235" spans="1:21" x14ac:dyDescent="0.25">
@@ -31800,12 +31801,12 @@
         <v>4.5925892192275302E-4</v>
       </c>
       <c r="T235" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>15666.01</v>
       </c>
       <c r="U235" s="65">
-        <f t="shared" si="7"/>
-        <v>100.42314102564103</v>
+        <f t="shared" si="9"/>
+        <v>86.076978021978022</v>
       </c>
     </row>
     <row r="236" spans="1:21" x14ac:dyDescent="0.25">
@@ -31860,12 +31861,12 @@
         <v>1.4694128076498352E-2</v>
       </c>
       <c r="T236" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>251467.49</v>
       </c>
       <c r="U236" s="65">
-        <f t="shared" si="7"/>
-        <v>1611.9710897435898</v>
+        <f t="shared" si="9"/>
+        <v>1381.6895054945055</v>
       </c>
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.25">
@@ -31920,12 +31921,12 @@
         <v>4.9512318175823971E-3</v>
       </c>
       <c r="T237" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>89035.35</v>
       </c>
       <c r="U237" s="65">
-        <f t="shared" si="7"/>
-        <v>570.73942307692312</v>
+        <f t="shared" si="9"/>
+        <v>489.20521978021981</v>
       </c>
     </row>
     <row r="238" spans="1:21" x14ac:dyDescent="0.25">
@@ -31980,12 +31981,12 @@
         <v>3.0752979911078217E-4</v>
       </c>
       <c r="T238" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>4245.9000000000005</v>
       </c>
       <c r="U238" s="65">
-        <f t="shared" si="7"/>
-        <v>27.217307692307696</v>
+        <f t="shared" si="9"/>
+        <v>23.329120879120882</v>
       </c>
     </row>
     <row r="239" spans="1:21" x14ac:dyDescent="0.25">
@@ -32040,12 +32041,12 @@
         <v>6.7712660580281439E-4</v>
       </c>
       <c r="T239" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>15915</v>
       </c>
       <c r="U239" s="65">
-        <f t="shared" si="7"/>
-        <v>102.01923076923077</v>
+        <f t="shared" si="9"/>
+        <v>87.445054945054949</v>
       </c>
     </row>
     <row r="240" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
@@ -32100,11 +32101,11 @@
         <v>0</v>
       </c>
       <c r="T240" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U240" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -32166,12 +32167,12 @@
         <v>7.6720440641868184E-2</v>
       </c>
       <c r="T241" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1573788.62</v>
       </c>
       <c r="U241" s="65">
-        <f t="shared" si="7"/>
-        <v>10088.38858974359</v>
+        <f t="shared" si="9"/>
+        <v>8647.190219780221</v>
       </c>
     </row>
     <row r="242" spans="1:21" x14ac:dyDescent="0.25">
@@ -32196,11 +32197,11 @@
       <c r="Q242" s="57"/>
       <c r="R242" s="58"/>
       <c r="T242" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U242" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -32256,11 +32257,11 @@
         <v>0</v>
       </c>
       <c r="T243" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U243" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -32316,12 +32317,12 @@
         <v>3.616383706108434E-4</v>
       </c>
       <c r="T244" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>8193.66</v>
       </c>
       <c r="U244" s="65">
-        <f t="shared" si="7"/>
-        <v>52.52346153846154</v>
+        <f t="shared" si="9"/>
+        <v>45.020109890109893</v>
       </c>
     </row>
     <row r="245" spans="1:21" x14ac:dyDescent="0.25">
@@ -32376,12 +32377,12 @@
         <v>7.371915464067342E-4</v>
       </c>
       <c r="T245" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>11447.34</v>
       </c>
       <c r="U245" s="65">
-        <f t="shared" si="7"/>
-        <v>73.380384615384614</v>
+        <f t="shared" si="9"/>
+        <v>62.89747252747253</v>
       </c>
     </row>
     <row r="246" spans="1:21" x14ac:dyDescent="0.25">
@@ -32436,11 +32437,11 @@
         <v>0</v>
       </c>
       <c r="T246" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U246" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -32496,12 +32497,12 @@
         <v>4.6616795832914804E-3</v>
       </c>
       <c r="T247" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>80105.239999999991</v>
       </c>
       <c r="U247" s="65">
-        <f t="shared" si="7"/>
-        <v>513.49512820512814</v>
+        <f t="shared" si="9"/>
+        <v>440.13868131868128</v>
       </c>
     </row>
     <row r="248" spans="1:21" x14ac:dyDescent="0.25">
@@ -32556,12 +32557,12 @@
         <v>8.6108812756460242E-4</v>
       </c>
       <c r="T248" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>12975.35</v>
       </c>
       <c r="U248" s="65">
-        <f t="shared" si="7"/>
-        <v>83.17532051282052</v>
+        <f t="shared" si="9"/>
+        <v>71.29313186813188</v>
       </c>
     </row>
     <row r="249" spans="1:21" x14ac:dyDescent="0.25">
@@ -32616,12 +32617,12 @@
         <v>1.9358580654461215E-3</v>
       </c>
       <c r="T249" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>41999.13</v>
       </c>
       <c r="U249" s="65">
-        <f t="shared" si="7"/>
-        <v>269.22519230769228</v>
+        <f t="shared" si="9"/>
+        <v>230.76445054945052</v>
       </c>
     </row>
     <row r="250" spans="1:21" x14ac:dyDescent="0.25">
@@ -32676,12 +32677,12 @@
         <v>2.0814256292736874E-3</v>
       </c>
       <c r="T250" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>79002.75</v>
       </c>
       <c r="U250" s="65">
-        <f t="shared" si="7"/>
-        <v>506.42788461538458</v>
+        <f t="shared" si="9"/>
+        <v>434.08104395604397</v>
       </c>
     </row>
     <row r="251" spans="1:21" x14ac:dyDescent="0.25">
@@ -32736,11 +32737,11 @@
         <v>0</v>
       </c>
       <c r="T251" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U251" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -32802,12 +32803,12 @@
         <v>1.063888132259347E-2</v>
       </c>
       <c r="T252" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>233723.46999999997</v>
       </c>
       <c r="U252" s="65">
-        <f t="shared" si="7"/>
-        <v>1498.2273717948717</v>
+        <f t="shared" si="9"/>
+        <v>1284.1948901098899</v>
       </c>
     </row>
     <row r="253" spans="1:21" x14ac:dyDescent="0.25">
@@ -32832,11 +32833,11 @@
       <c r="Q253" s="57"/>
       <c r="R253" s="58"/>
       <c r="T253" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U253" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -32892,11 +32893,11 @@
         <v>0</v>
       </c>
       <c r="T254" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U254" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -32952,11 +32953,11 @@
         <v>0</v>
       </c>
       <c r="T255" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U255" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -33012,12 +33013,12 @@
         <v>0</v>
       </c>
       <c r="T256" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1063138.51</v>
       </c>
       <c r="U256" s="65">
-        <f t="shared" si="7"/>
-        <v>6814.9904487179483</v>
+        <f t="shared" si="9"/>
+        <v>5841.4203846153841</v>
       </c>
     </row>
     <row r="257" spans="1:21" x14ac:dyDescent="0.25">
@@ -33072,11 +33073,11 @@
         <v>0</v>
       </c>
       <c r="T257" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U257" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -33132,12 +33133,12 @@
         <v>9.268623300305227E-3</v>
       </c>
       <c r="T258" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>119292.94</v>
       </c>
       <c r="U258" s="65">
-        <f t="shared" si="7"/>
-        <v>764.69833333333338</v>
+        <f t="shared" si="9"/>
+        <v>655.45571428571441</v>
       </c>
     </row>
     <row r="259" spans="1:21" x14ac:dyDescent="0.25">
@@ -33192,11 +33193,11 @@
         <v>0</v>
       </c>
       <c r="T259" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U259" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -33252,11 +33253,11 @@
         <v>0</v>
       </c>
       <c r="T260" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U260" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -33312,12 +33313,12 @@
         <v>1.3057407544048671E-2</v>
       </c>
       <c r="T261" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>231487</v>
       </c>
       <c r="U261" s="65">
-        <f t="shared" si="7"/>
-        <v>1483.8910256410256</v>
+        <f t="shared" si="9"/>
+        <v>1271.9065934065934</v>
       </c>
     </row>
     <row r="262" spans="1:21" x14ac:dyDescent="0.25">
@@ -33372,12 +33373,12 @@
         <v>1.0248208583885324E-3</v>
       </c>
       <c r="T262" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>19370.47</v>
       </c>
       <c r="U262" s="65">
-        <f t="shared" si="7"/>
-        <v>124.16967948717949</v>
+        <f t="shared" si="9"/>
+        <v>106.43115384615385</v>
       </c>
     </row>
     <row r="263" spans="1:21" x14ac:dyDescent="0.25">
@@ -33438,12 +33439,12 @@
         <v>2.3350851702742426E-2</v>
       </c>
       <c r="T263" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1433288.9200000002</v>
       </c>
       <c r="U263" s="65">
-        <f t="shared" si="7"/>
-        <v>9187.7494871794879</v>
+        <f t="shared" si="9"/>
+        <v>7875.213846153847</v>
       </c>
     </row>
     <row r="264" spans="1:21" x14ac:dyDescent="0.25">
@@ -33468,11 +33469,11 @@
       <c r="Q264" s="57"/>
       <c r="R264" s="58"/>
       <c r="T264" s="65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U264" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -33528,11 +33529,11 @@
         <v>0</v>
       </c>
       <c r="T265" s="65">
-        <f t="shared" ref="T265:T327" si="8">IFERROR(B265+E265+H265+K265+N265+Q265, "NA")</f>
+        <f t="shared" ref="T265:T327" si="10">IFERROR(B265+E265+H265+K265+N265+Q265, "NA")</f>
         <v>0</v>
       </c>
       <c r="U265" s="65">
-        <f t="shared" ref="U265:U327" si="9">(T265/$V$1)/6</f>
+        <f t="shared" ref="U265:U327" si="11">(T265/$V$1)/7</f>
         <v>0</v>
       </c>
     </row>
@@ -33588,11 +33589,11 @@
         <v>0</v>
       </c>
       <c r="T266" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U266" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -33648,11 +33649,11 @@
         <v>0</v>
       </c>
       <c r="T267" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U267" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -33708,12 +33709,12 @@
         <v>-6.006584930196221E-3</v>
       </c>
       <c r="T268" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>-71131.3</v>
       </c>
       <c r="U268" s="65">
-        <f t="shared" si="9"/>
-        <v>-455.96987179487178</v>
+        <f t="shared" si="11"/>
+        <v>-390.83131868131869</v>
       </c>
     </row>
     <row r="269" spans="1:21" x14ac:dyDescent="0.25">
@@ -33768,11 +33769,11 @@
         <v>0</v>
       </c>
       <c r="T269" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U269" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -33828,11 +33829,11 @@
         <v>0</v>
       </c>
       <c r="T270" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U270" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -33888,11 +33889,11 @@
         <v>0</v>
       </c>
       <c r="T271" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U271" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -33948,11 +33949,11 @@
         <v>0</v>
       </c>
       <c r="T272" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U272" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -34008,11 +34009,11 @@
         <v>0</v>
       </c>
       <c r="T273" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U273" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -34068,11 +34069,11 @@
         <v>0</v>
       </c>
       <c r="T274" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U274" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -34128,11 +34129,11 @@
         <v>0</v>
       </c>
       <c r="T275" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U275" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -34188,11 +34189,11 @@
         <v>0</v>
       </c>
       <c r="T276" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U276" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -34248,11 +34249,11 @@
         <v>0</v>
       </c>
       <c r="T277" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U277" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -34308,12 +34309,12 @@
         <v>-3.3098933403068194E-2</v>
       </c>
       <c r="T278" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>-734270.89</v>
       </c>
       <c r="U278" s="65">
-        <f t="shared" si="9"/>
-        <v>-4706.8646794871793</v>
+        <f t="shared" si="11"/>
+        <v>-4034.4554395604396</v>
       </c>
     </row>
     <row r="279" spans="1:21" x14ac:dyDescent="0.25">
@@ -34368,11 +34369,11 @@
         <v>0</v>
       </c>
       <c r="T279" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U279" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -34428,11 +34429,11 @@
         <v>0</v>
       </c>
       <c r="T280" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U280" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -34488,11 +34489,11 @@
         <v>0</v>
       </c>
       <c r="T281" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U281" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -34548,11 +34549,11 @@
         <v>0</v>
       </c>
       <c r="T282" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U282" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -34614,12 +34615,12 @@
         <v>-3.9105518333264415E-2</v>
       </c>
       <c r="T283" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>-805402.19</v>
       </c>
       <c r="U283" s="65">
-        <f t="shared" si="9"/>
-        <v>-5162.8345512820515</v>
+        <f t="shared" si="11"/>
+        <v>-4425.2867582417584</v>
       </c>
     </row>
     <row r="284" spans="1:21" x14ac:dyDescent="0.25">
@@ -34680,12 +34681,12 @@
         <v>7.1604655333939671E-2</v>
       </c>
       <c r="T284" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>2435398.8199999998</v>
       </c>
       <c r="U284" s="65">
-        <f t="shared" si="9"/>
-        <v>15611.530897435898</v>
+        <f t="shared" si="11"/>
+        <v>13381.312197802197</v>
       </c>
     </row>
     <row r="285" spans="1:21" x14ac:dyDescent="0.25">
@@ -34710,11 +34711,11 @@
       <c r="Q285" s="57"/>
       <c r="R285" s="58"/>
       <c r="T285" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U285" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -34740,11 +34741,11 @@
       <c r="Q286" s="57"/>
       <c r="R286" s="58"/>
       <c r="T286" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U286" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -34800,11 +34801,11 @@
         <v>0</v>
       </c>
       <c r="T287" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U287" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -34860,11 +34861,11 @@
         <v>0</v>
       </c>
       <c r="T288" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U288" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -34920,12 +34921,12 @@
         <v>8.6846059997263136E-3</v>
       </c>
       <c r="T289" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>105125.72</v>
       </c>
       <c r="U289" s="65">
-        <f t="shared" si="9"/>
-        <v>673.88282051282056</v>
+        <f t="shared" si="11"/>
+        <v>577.61384615384611</v>
       </c>
     </row>
     <row r="290" spans="1:21" x14ac:dyDescent="0.25">
@@ -34980,12 +34981,12 @@
         <v>5.1822038066193482E-2</v>
       </c>
       <c r="T290" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1134863.3500000001</v>
       </c>
       <c r="U290" s="65">
-        <f t="shared" si="9"/>
-        <v>7274.7650641025648</v>
+        <f t="shared" si="11"/>
+        <v>6235.5129120879128</v>
       </c>
     </row>
     <row r="291" spans="1:21" x14ac:dyDescent="0.25">
@@ -35040,12 +35041,12 @@
         <v>0</v>
       </c>
       <c r="T291" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>550</v>
       </c>
       <c r="U291" s="65">
-        <f t="shared" si="9"/>
-        <v>3.5256410256410255</v>
+        <f t="shared" si="11"/>
+        <v>3.0219780219780219</v>
       </c>
     </row>
     <row r="292" spans="1:21" x14ac:dyDescent="0.25">
@@ -35100,12 +35101,12 @@
         <v>1.1942138986315326E-3</v>
       </c>
       <c r="T292" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>16260.03</v>
       </c>
       <c r="U292" s="65">
-        <f t="shared" si="9"/>
-        <v>104.23096153846154</v>
+        <f t="shared" si="11"/>
+        <v>89.340824175824181</v>
       </c>
     </row>
     <row r="293" spans="1:21" x14ac:dyDescent="0.25">
@@ -35160,12 +35161,12 @@
         <v>1.1160893172555298E-3</v>
       </c>
       <c r="T293" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>5300.1900000000005</v>
       </c>
       <c r="U293" s="65">
-        <f t="shared" si="9"/>
-        <v>33.975576923076922</v>
+        <f t="shared" si="11"/>
+        <v>29.121923076923078</v>
       </c>
     </row>
     <row r="294" spans="1:21" x14ac:dyDescent="0.25">
@@ -35220,12 +35221,12 @@
         <v>4.2173848662285683E-3</v>
       </c>
       <c r="T294" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>87695.09</v>
       </c>
       <c r="U294" s="65">
-        <f t="shared" si="9"/>
-        <v>562.1480128205128</v>
+        <f t="shared" si="11"/>
+        <v>481.84115384615382</v>
       </c>
     </row>
     <row r="295" spans="1:21" x14ac:dyDescent="0.25">
@@ -35280,12 +35281,12 @@
         <v>2.9109115839501509E-4</v>
       </c>
       <c r="T295" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>6158.01</v>
       </c>
       <c r="U295" s="65">
-        <f t="shared" si="9"/>
-        <v>39.474423076923081</v>
+        <f t="shared" si="11"/>
+        <v>33.835219780219781</v>
       </c>
     </row>
     <row r="296" spans="1:21" x14ac:dyDescent="0.25">
@@ -35340,11 +35341,11 @@
         <v>0</v>
       </c>
       <c r="T296" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U296" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -35400,12 +35401,12 @@
         <v>0</v>
       </c>
       <c r="T297" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>2681.12</v>
       </c>
       <c r="U297" s="65">
-        <f t="shared" si="9"/>
-        <v>17.186666666666664</v>
+        <f t="shared" si="11"/>
+        <v>14.73142857142857</v>
       </c>
     </row>
     <row r="298" spans="1:21" x14ac:dyDescent="0.25">
@@ -35460,11 +35461,11 @@
         <v>0</v>
       </c>
       <c r="T298" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U298" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -35520,11 +35521,11 @@
         <v>0</v>
       </c>
       <c r="T299" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U299" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -35580,11 +35581,11 @@
         <v>0</v>
       </c>
       <c r="T300" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U300" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -35640,11 +35641,11 @@
         <v>0</v>
       </c>
       <c r="T301" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U301" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -35700,11 +35701,11 @@
         <v>0</v>
       </c>
       <c r="T302" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U302" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -35760,11 +35761,11 @@
         <v>0</v>
       </c>
       <c r="T303" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U303" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -35820,11 +35821,11 @@
         <v>0</v>
       </c>
       <c r="T304" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U304" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -35880,11 +35881,11 @@
         <v>0</v>
       </c>
       <c r="T305" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U305" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -35940,11 +35941,11 @@
         <v>0</v>
       </c>
       <c r="T306" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U306" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -36000,11 +36001,11 @@
         <v>0</v>
       </c>
       <c r="T307" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U307" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -36060,11 +36061,11 @@
         <v>0</v>
       </c>
       <c r="T308" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U308" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -36120,11 +36121,11 @@
         <v>0</v>
       </c>
       <c r="T309" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U309" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -36180,11 +36181,11 @@
         <v>0</v>
       </c>
       <c r="T310" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U310" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -36240,12 +36241,12 @@
         <v>0</v>
       </c>
       <c r="T311" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>5571.22</v>
       </c>
       <c r="U311" s="65">
-        <f t="shared" si="9"/>
-        <v>35.71294871794872</v>
+        <f t="shared" si="11"/>
+        <v>30.611098901098902</v>
       </c>
     </row>
     <row r="312" spans="1:21" x14ac:dyDescent="0.25">
@@ -36300,11 +36301,11 @@
         <v>0</v>
       </c>
       <c r="T312" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U312" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -36360,11 +36361,11 @@
         <v>0</v>
       </c>
       <c r="T313" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U313" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -36426,12 +36427,12 @@
         <v>6.7325423306430432E-2</v>
       </c>
       <c r="T314" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1364204.7299999997</v>
       </c>
       <c r="U314" s="65">
-        <f t="shared" si="9"/>
-        <v>8744.9021153846134</v>
+        <f t="shared" si="11"/>
+        <v>7495.6303846153833</v>
       </c>
     </row>
     <row r="315" spans="1:21" x14ac:dyDescent="0.25">
@@ -36456,11 +36457,11 @@
       <c r="Q315" s="57"/>
       <c r="R315" s="58"/>
       <c r="T315" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U315" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -36516,11 +36517,11 @@
         <v>0</v>
       </c>
       <c r="T316" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U316" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -36576,11 +36577,11 @@
         <v>0</v>
       </c>
       <c r="T317" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U317" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -36636,11 +36637,11 @@
         <v>0</v>
       </c>
       <c r="T318" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U318" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -36696,12 +36697,12 @@
         <v>0</v>
       </c>
       <c r="T319" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>2846.34</v>
       </c>
       <c r="U319" s="65">
-        <f t="shared" si="9"/>
-        <v>18.245769230769231</v>
+        <f t="shared" si="11"/>
+        <v>15.639230769230769</v>
       </c>
     </row>
     <row r="320" spans="1:21" x14ac:dyDescent="0.25">
@@ -36756,11 +36757,11 @@
         <v>0</v>
       </c>
       <c r="T320" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U320" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -36816,11 +36817,11 @@
         <v>0</v>
       </c>
       <c r="T321" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U321" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -36876,12 +36877,12 @@
         <v>3.5966854775759883E-4</v>
       </c>
       <c r="T322" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>19457.71</v>
       </c>
       <c r="U322" s="65">
-        <f t="shared" si="9"/>
-        <v>124.72891025641024</v>
+        <f t="shared" si="11"/>
+        <v>106.9104945054945</v>
       </c>
     </row>
     <row r="323" spans="1:21" x14ac:dyDescent="0.25">
@@ -36936,11 +36937,11 @@
         <v>0</v>
       </c>
       <c r="T323" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U323" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -37002,12 +37003,12 @@
         <v>3.5966854775759883E-4</v>
       </c>
       <c r="T324" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>22304.05</v>
       </c>
       <c r="U324" s="65">
-        <f t="shared" si="9"/>
-        <v>142.97467948717949</v>
+        <f t="shared" si="11"/>
+        <v>122.54972527472526</v>
       </c>
     </row>
     <row r="325" spans="1:21" x14ac:dyDescent="0.25">
@@ -37068,12 +37069,12 @@
         <v>6.7685091854188043E-2</v>
       </c>
       <c r="T325" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1386508.7799999998</v>
       </c>
       <c r="U325" s="65">
-        <f t="shared" si="9"/>
-        <v>8887.8767948717941</v>
+        <f t="shared" si="11"/>
+        <v>7618.1801098901096</v>
       </c>
     </row>
     <row r="326" spans="1:21" x14ac:dyDescent="0.25">
@@ -37134,12 +37135,12 @@
         <v>0.25954488216162042</v>
       </c>
       <c r="T326" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>4772398.1999999993</v>
       </c>
       <c r="U326" s="65">
-        <f t="shared" si="9"/>
-        <v>30592.29615384615</v>
+        <f t="shared" si="11"/>
+        <v>26221.968131868129</v>
       </c>
     </row>
     <row r="327" spans="1:21" x14ac:dyDescent="0.25">
@@ -37176,12 +37177,12 @@
       </c>
       <c r="R327" s="75"/>
       <c r="T327" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>21973011.540000003</v>
       </c>
       <c r="U327" s="65">
-        <f t="shared" si="9"/>
-        <v>140852.63807692309</v>
+        <f t="shared" si="11"/>
+        <v>120730.83263736265</v>
       </c>
     </row>
     <row r="330" spans="1:21" x14ac:dyDescent="0.25">
